--- a/jira_export_2026-07-08.xlsx
+++ b/jira_export_2026-07-08.xlsx
@@ -729,7 +729,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>10,283 €</t>
+          <t>10,733 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -743,7 +743,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -776,7 +776,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>7,864 €</t>
+          <t>8,314 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -824,7 +824,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>175 h</t>
+          <t>193 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -838,7 +838,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>73.0%</t>
+          <t>80.6%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -895,7 +895,7 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
@@ -909,7 +909,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>254</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -942,7 +942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P148"/>
+  <dimension ref="A1:P149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="12" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L7" s="12" t="inlineStr"/>
       <c r="M7" s="12" t="inlineStr"/>
@@ -1598,7 +1598,7 @@
         <v>1</v>
       </c>
       <c r="K12" s="15" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="L12" s="15" t="inlineStr">
         <is>
@@ -2619,9 +2619,9 @@
         </is>
       </c>
       <c r="N26" s="16" t="n">
-        <v>657.3</v>
-      </c>
-      <c r="O26" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="16" t="n">
         <v>219.1</v>
       </c>
       <c r="P26" s="16" t="n">
@@ -2907,9 +2907,9 @@
         </is>
       </c>
       <c r="N30" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="16" t="n">
+        <v>920</v>
+      </c>
+      <c r="O30" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P30" s="16" t="n">
@@ -5493,8 +5493,8 @@
       <c r="N66" s="16" t="n">
         <v>450</v>
       </c>
-      <c r="O66" s="17" t="n">
-        <v>0</v>
+      <c r="O66" s="16" t="n">
+        <v>450</v>
       </c>
       <c r="P66" s="16" t="n">
         <v>0</v>
@@ -8272,7 +8272,7 @@
         <v>8</v>
       </c>
       <c r="K105" s="12" t="n">
-        <v>0.75</v>
+        <v>4.25</v>
       </c>
       <c r="L105" s="12" t="inlineStr">
         <is>
@@ -9125,22 +9125,22 @@
     <row r="118">
       <c r="A118" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-22996</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C118" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D118" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E118" s="15" t="n">
@@ -9158,28 +9158,28 @@
       </c>
       <c r="H118" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I118" s="15" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J118" s="15" t="n">
         <v>12</v>
       </c>
       <c r="K118" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L118" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28051</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M118" s="15" t="inlineStr">
         <is>
-          <t>487190</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N118" s="16" t="n">
@@ -9195,22 +9195,22 @@
     <row r="119">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-22996</t>
         </is>
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E119" s="12" t="n">
@@ -9228,28 +9228,28 @@
       </c>
       <c r="H119" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I119" s="12" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="J119" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K119" s="12" t="n">
-        <v>0.12</v>
+        <v>2</v>
       </c>
       <c r="L119" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-28051</t>
         </is>
       </c>
       <c r="M119" s="12" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>487190</t>
         </is>
       </c>
       <c r="N119" s="13" t="n">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="L120" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M120" s="15" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N120" s="16" t="n">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E121" s="12" t="n">
@@ -9384,12 +9384,12 @@
       </c>
       <c r="L121" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M121" s="12" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N121" s="13" t="n">
@@ -9420,7 +9420,7 @@
       </c>
       <c r="D122" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E122" s="15" t="n">
@@ -9454,12 +9454,12 @@
       </c>
       <c r="L122" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M122" s="15" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N122" s="16" t="n">
@@ -9475,12 +9475,12 @@
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-22496</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - LITTERALIS Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
@@ -9490,7 +9490,7 @@
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E123" s="12" t="n">
@@ -9508,28 +9508,28 @@
       </c>
       <c r="H123" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I123" s="12" t="inlineStr">
         <is>
-          <t>23/06/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J123" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K123" s="12" t="n">
-        <v>0.5</v>
+        <v>0.12</v>
       </c>
       <c r="L123" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27371</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M123" s="12" t="inlineStr">
         <is>
-          <t>481817</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N123" s="13" t="n">
@@ -9545,22 +9545,22 @@
     <row r="124">
       <c r="A124" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21546</t>
+          <t>PDMDEP-22496</t>
         </is>
       </c>
       <c r="B124" s="15" t="inlineStr">
         <is>
-          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
+          <t>[VILLEJUIF] - LITTERALIS Pastell</t>
         </is>
       </c>
       <c r="C124" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D124" s="15" t="inlineStr">
         <is>
-          <t>VILLEURBANNE</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E124" s="15" t="n">
@@ -9568,7 +9568,7 @@
       </c>
       <c r="F124" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G124" s="15" t="inlineStr">
@@ -9583,29 +9583,29 @@
       </c>
       <c r="I124" s="15" t="inlineStr">
         <is>
-          <t>05/05/2025</t>
+          <t>23/06/2025</t>
         </is>
       </c>
       <c r="J124" s="15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K124" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L124" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28038</t>
+          <t>PDMDEP-27371</t>
         </is>
       </c>
       <c r="M124" s="15" t="inlineStr">
         <is>
-          <t>478867</t>
+          <t>481817</t>
         </is>
       </c>
       <c r="N124" s="16" t="n">
-        <v>482.72</v>
-      </c>
-      <c r="O124" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P124" s="16" t="n">
@@ -9615,22 +9615,22 @@
     <row r="125">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21546</t>
         </is>
       </c>
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>VILLEURBANNE</t>
         </is>
       </c>
       <c r="E125" s="12" t="n">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="F125" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G125" s="12" t="inlineStr">
@@ -9648,34 +9648,34 @@
       </c>
       <c r="H125" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I125" s="12" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="J125" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K125" s="12" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L125" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-28038</t>
         </is>
       </c>
       <c r="M125" s="12" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>478867</t>
         </is>
       </c>
       <c r="N125" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O125" s="13" t="n">
+        <v>482.72</v>
+      </c>
+      <c r="O125" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P125" s="13" t="n">
@@ -9685,22 +9685,22 @@
     <row r="126">
       <c r="A126" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C126" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D126" s="15" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E126" s="15" t="n">
@@ -9718,34 +9718,34 @@
       </c>
       <c r="H126" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I126" s="15" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J126" s="15" t="n">
         <v>15</v>
       </c>
       <c r="K126" s="15" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L126" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M126" s="15" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N126" s="16" t="n">
-        <v>250</v>
-      </c>
-      <c r="O126" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P126" s="16" t="n">
@@ -9755,22 +9755,22 @@
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E127" s="12" t="n">
@@ -9793,27 +9793,27 @@
       </c>
       <c r="I127" s="12" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J127" s="12" t="n">
         <v>15</v>
       </c>
       <c r="K127" s="12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L127" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M127" s="12" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N127" s="13" t="n">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="O127" s="17" t="n">
         <v>0</v>
@@ -9825,22 +9825,22 @@
     <row r="128">
       <c r="A128" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C128" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D128" s="15" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E128" s="15" t="n">
@@ -9856,24 +9856,36 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H128" s="15" t="inlineStr"/>
+      <c r="H128" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I128" s="15" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J128" s="15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K128" s="15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L128" s="15" t="inlineStr"/>
-      <c r="M128" s="15" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L128" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="M128" s="15" t="inlineStr">
+        <is>
+          <t>475575</t>
+        </is>
+      </c>
       <c r="N128" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O128" s="16" t="n">
+        <v>230</v>
+      </c>
+      <c r="O128" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P128" s="16" t="n">
@@ -9883,22 +9895,22 @@
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E129" s="12" t="n">
@@ -9914,14 +9926,10 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H129" s="12" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+      <c r="H129" s="12" t="inlineStr"/>
       <c r="I129" s="12" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J129" s="12" t="n">
@@ -9930,16 +9938,8 @@
       <c r="K129" s="12" t="n">
         <v>0.25</v>
       </c>
-      <c r="L129" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-27568</t>
-        </is>
-      </c>
-      <c r="M129" s="12" t="inlineStr">
-        <is>
-          <t>471958</t>
-        </is>
-      </c>
+      <c r="L129" s="12" t="inlineStr"/>
+      <c r="M129" s="12" t="inlineStr"/>
       <c r="N129" s="13" t="n">
         <v>0</v>
       </c>
@@ -9953,12 +9953,12 @@
     <row r="130">
       <c r="A130" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C130" s="15" t="inlineStr">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="D130" s="15" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E130" s="15" t="n">
@@ -9986,28 +9986,28 @@
       </c>
       <c r="H130" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I130" s="15" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J130" s="15" t="n">
         <v>16</v>
       </c>
       <c r="K130" s="15" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="L130" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27377</t>
+          <t>PDMDEP-27568</t>
         </is>
       </c>
       <c r="M130" s="15" t="inlineStr">
         <is>
-          <t>478048</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="N130" s="16" t="n">
@@ -10023,12 +10023,12 @@
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-19385</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
@@ -10038,7 +10038,7 @@
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARCUEIL</t>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
         </is>
       </c>
       <c r="E131" s="12" t="n">
@@ -10061,23 +10061,23 @@
       </c>
       <c r="I131" s="12" t="inlineStr">
         <is>
-          <t>24/02/2025</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J131" s="12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K131" s="12" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L131" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27535</t>
+          <t>PDMDEP-27377</t>
         </is>
       </c>
       <c r="M131" s="12" t="inlineStr">
         <is>
-          <t>465345</t>
+          <t>478048</t>
         </is>
       </c>
       <c r="N131" s="13" t="n">
@@ -10093,12 +10093,12 @@
     <row r="132">
       <c r="A132" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-19385</t>
         </is>
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
         </is>
       </c>
       <c r="C132" s="15" t="inlineStr">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="D132" s="15" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>COMMUNE D'ARCUEIL</t>
         </is>
       </c>
       <c r="E132" s="15" t="n">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="G132" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H132" s="15" t="inlineStr">
@@ -10131,17 +10131,25 @@
       </c>
       <c r="I132" s="15" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>24/02/2025</t>
         </is>
       </c>
       <c r="J132" s="15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K132" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L132" s="15" t="inlineStr"/>
-      <c r="M132" s="15" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L132" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27535</t>
+        </is>
+      </c>
+      <c r="M132" s="15" t="inlineStr">
+        <is>
+          <t>465345</t>
+        </is>
+      </c>
       <c r="N132" s="16" t="n">
         <v>0</v>
       </c>
@@ -10155,22 +10163,22 @@
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E133" s="12" t="n">
@@ -10178,44 +10186,36 @@
       </c>
       <c r="F133" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H133" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I133" s="12" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J133" s="12" t="n">
         <v>19</v>
       </c>
       <c r="K133" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L133" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M133" s="12" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="L133" s="12" t="inlineStr"/>
+      <c r="M133" s="12" t="inlineStr"/>
       <c r="N133" s="13" t="n">
-        <v>240</v>
-      </c>
-      <c r="O133" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P133" s="13" t="n">
@@ -10225,22 +10225,22 @@
     <row r="134">
       <c r="A134" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B134" s="15" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C134" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D134" s="15" t="inlineStr">
         <is>
-          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E134" s="15" t="n">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="F134" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G134" s="15" t="inlineStr">
@@ -10258,34 +10258,34 @@
       </c>
       <c r="H134" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I134" s="15" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J134" s="15" t="n">
         <v>19</v>
       </c>
       <c r="K134" s="15" t="n">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="L134" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34362</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M134" s="15" t="inlineStr">
         <is>
-          <t>458057</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N134" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O134" s="16" t="n">
+        <v>240</v>
+      </c>
+      <c r="O134" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P134" s="16" t="n">
@@ -10310,7 +10310,7 @@
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
         </is>
       </c>
       <c r="E135" s="12" t="n">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="L135" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28020</t>
+          <t>PDMDEP-34362</t>
         </is>
       </c>
       <c r="M135" s="12" t="inlineStr">
@@ -10365,22 +10365,22 @@
     <row r="136">
       <c r="A136" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-16868</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B136" s="15" t="inlineStr">
         <is>
-          <t>[Limoges] migration placier</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C136" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D136" s="15" t="inlineStr">
         <is>
-          <t>Limoges</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E136" s="15" t="n">
@@ -10388,32 +10388,40 @@
       </c>
       <c r="F136" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G136" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H136" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I136" s="15" t="inlineStr">
         <is>
-          <t>26/09/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J136" s="15" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K136" s="15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L136" s="15" t="inlineStr"/>
-      <c r="M136" s="15" t="inlineStr"/>
+        <v>0.62</v>
+      </c>
+      <c r="L136" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28020</t>
+        </is>
+      </c>
+      <c r="M136" s="15" t="inlineStr">
+        <is>
+          <t>458057</t>
+        </is>
+      </c>
       <c r="N136" s="16" t="n">
         <v>0</v>
       </c>
@@ -10427,22 +10435,22 @@
     <row r="137">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-16868</t>
         </is>
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[Limoges] migration placier</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>Limoges</t>
         </is>
       </c>
       <c r="E137" s="12" t="n">
@@ -10450,7 +10458,7 @@
       </c>
       <c r="F137" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G137" s="12" t="inlineStr">
@@ -10460,19 +10468,19 @@
       </c>
       <c r="H137" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I137" s="12" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>26/09/2024</t>
         </is>
       </c>
       <c r="J137" s="12" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K137" s="12" t="n">
-        <v>0.25</v>
+        <v>2.5</v>
       </c>
       <c r="L137" s="12" t="inlineStr"/>
       <c r="M137" s="12" t="inlineStr"/>
@@ -10489,22 +10497,22 @@
     <row r="138">
       <c r="A138" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14551</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>[Perpignan] Interface formulaire</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C138" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D138" s="15" t="inlineStr">
         <is>
-          <t>[Perpignan]</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E138" s="15" t="n">
@@ -10527,14 +10535,14 @@
       </c>
       <c r="I138" s="15" t="inlineStr">
         <is>
-          <t>14/03/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J138" s="15" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K138" s="15" t="n">
-        <v>1.25</v>
+        <v>0.25</v>
       </c>
       <c r="L138" s="15" t="inlineStr"/>
       <c r="M138" s="15" t="inlineStr"/>
@@ -10551,12 +10559,12 @@
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14254</t>
+          <t>PDMDEP-14551</t>
         </is>
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
+          <t>[Perpignan] Interface formulaire</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
@@ -10566,7 +10574,7 @@
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>Dijon métropole</t>
+          <t>[Perpignan]</t>
         </is>
       </c>
       <c r="E139" s="12" t="n">
@@ -10589,14 +10597,14 @@
       </c>
       <c r="I139" s="12" t="inlineStr">
         <is>
-          <t>19/02/2024</t>
+          <t>14/03/2024</t>
         </is>
       </c>
       <c r="J139" s="12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K139" s="12" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="L139" s="12" t="inlineStr"/>
       <c r="M139" s="12" t="inlineStr"/>
@@ -10613,22 +10621,22 @@
     <row r="140">
       <c r="A140" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14095</t>
+          <t>PDMDEP-14254</t>
         </is>
       </c>
       <c r="B140" s="15" t="inlineStr">
         <is>
-          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
+          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
         </is>
       </c>
       <c r="C140" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D140" s="15" t="inlineStr">
         <is>
-          <t>CC du Pays Sabolien</t>
+          <t>Dijon métropole</t>
         </is>
       </c>
       <c r="E140" s="15" t="n">
@@ -10646,19 +10654,19 @@
       </c>
       <c r="H140" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I140" s="15" t="inlineStr">
         <is>
-          <t>31/01/2024</t>
+          <t>19/02/2024</t>
         </is>
       </c>
       <c r="J140" s="15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K140" s="15" t="n">
-        <v>6.75</v>
+        <v>0.75</v>
       </c>
       <c r="L140" s="15" t="inlineStr"/>
       <c r="M140" s="15" t="inlineStr"/>
@@ -10675,22 +10683,22 @@
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-14095</t>
         </is>
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>CC du Pays Sabolien</t>
         </is>
       </c>
       <c r="E141" s="12" t="n">
@@ -10703,35 +10711,27 @@
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H141" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I141" s="12" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>31/01/2024</t>
         </is>
       </c>
       <c r="J141" s="12" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K141" s="12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L141" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M141" s="12" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>6.75</v>
+      </c>
+      <c r="L141" s="12" t="inlineStr"/>
+      <c r="M141" s="12" t="inlineStr"/>
       <c r="N141" s="13" t="n">
         <v>0</v>
       </c>
@@ -10745,22 +10745,22 @@
     <row r="142">
       <c r="A142" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B142" s="15" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C142" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D142" s="15" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E142" s="15" t="n">
@@ -10773,27 +10773,35 @@
       </c>
       <c r="G142" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H142" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I142" s="15" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J142" s="15" t="n">
         <v>34</v>
       </c>
       <c r="K142" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L142" s="15" t="inlineStr"/>
-      <c r="M142" s="15" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L142" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M142" s="15" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N142" s="16" t="n">
         <v>0</v>
       </c>
@@ -10807,28 +10815,26 @@
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12241</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe]</t>
-        </is>
-      </c>
-      <c r="E143" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement de Littéralis Expert</t>
-        </is>
+          <t>LE MANS METROPOLE</t>
+        </is>
+      </c>
+      <c r="E143" s="12" t="n">
+        <v/>
       </c>
       <c r="F143" s="12" t="inlineStr">
         <is>
@@ -10847,14 +10853,14 @@
       </c>
       <c r="I143" s="12" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J143" s="12" t="n">
         <v>34</v>
       </c>
       <c r="K143" s="12" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L143" s="12" t="inlineStr"/>
       <c r="M143" s="12" t="inlineStr"/>
@@ -10871,12 +10877,12 @@
     <row r="144">
       <c r="A144" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12241</t>
         </is>
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C144" s="15" t="inlineStr">
@@ -10886,12 +10892,12 @@
       </c>
       <c r="D144" s="15" t="inlineStr">
         <is>
-          <t>CD14</t>
+          <t>[SM Routes de Guadeloupe]</t>
         </is>
       </c>
       <c r="E144" s="15" t="inlineStr">
         <is>
-          <t>Modélisation spécifique</t>
+          <t>Déploiement de Littéralis Expert</t>
         </is>
       </c>
       <c r="F144" s="15" t="inlineStr">
@@ -10906,7 +10912,7 @@
       </c>
       <c r="H144" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I144" s="15" t="inlineStr">
@@ -10918,7 +10924,7 @@
         <v>34</v>
       </c>
       <c r="K144" s="15" t="n">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="L144" s="15" t="inlineStr"/>
       <c r="M144" s="15" t="inlineStr"/>
@@ -10935,23 +10941,27 @@
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B145" s="12" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C145" s="12" t="inlineStr"/>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C145" s="12" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
+          <t>CD14</t>
         </is>
       </c>
       <c r="E145" s="12" t="inlineStr">
         <is>
-          <t>Déploiement Module AC</t>
+          <t>Modélisation spécifique</t>
         </is>
       </c>
       <c r="F145" s="12" t="inlineStr">
@@ -10966,19 +10976,19 @@
       </c>
       <c r="H145" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I145" s="12" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J145" s="12" t="n">
         <v>34</v>
       </c>
       <c r="K145" s="12" t="n">
-        <v>1.75</v>
+        <v>6.25</v>
       </c>
       <c r="L145" s="12" t="inlineStr"/>
       <c r="M145" s="12" t="inlineStr"/>
@@ -10995,21 +11005,25 @@
     <row r="146">
       <c r="A146" s="14" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C146" s="15" t="inlineStr"/>
       <c r="D146" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="E146" s="15" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E146" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F146" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11017,35 +11031,31 @@
       </c>
       <c r="G146" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H146" s="15" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H146" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I146" s="15" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J146" s="15" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="K146" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L146" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M146" s="15" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>1.75</v>
+      </c>
+      <c r="L146" s="15" t="inlineStr"/>
+      <c r="M146" s="15" t="inlineStr"/>
       <c r="N146" s="16" t="n">
-        <v>510.6</v>
-      </c>
-      <c r="O146" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O146" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P146" s="16" t="n">
@@ -11055,18 +11065,18 @@
     <row r="147">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>PSC-1228</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B147" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE MERLEVENEZ</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr"/>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE MERLEVENEZ</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E147" s="12" t="inlineStr"/>
@@ -11083,61 +11093,121 @@
       <c r="H147" s="12" t="inlineStr"/>
       <c r="I147" s="12" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J147" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K147" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L147" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M147" s="12" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N147" s="13" t="n">
+        <v>510.6</v>
+      </c>
+      <c r="O147" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P147" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="14" t="inlineStr">
+        <is>
+          <t>PSC-1228</t>
+        </is>
+      </c>
+      <c r="B148" s="15" t="inlineStr">
+        <is>
+          <t>MAIRIE DE MERLEVENEZ</t>
+        </is>
+      </c>
+      <c r="C148" s="15" t="inlineStr"/>
+      <c r="D148" s="15" t="inlineStr">
+        <is>
+          <t>MAIRIE DE MERLEVENEZ</t>
+        </is>
+      </c>
+      <c r="E148" s="15" t="inlineStr"/>
+      <c r="F148" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G148" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H148" s="15" t="inlineStr"/>
+      <c r="I148" s="15" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="J147" s="12" t="n">
+      <c r="J148" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="K147" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L147" s="12" t="inlineStr">
+      <c r="K148" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" s="15" t="inlineStr">
         <is>
           <t>PDMDEP-32829</t>
         </is>
       </c>
-      <c r="M147" s="12" t="inlineStr">
+      <c r="M148" s="15" t="inlineStr">
         <is>
           <t>00163534</t>
         </is>
       </c>
-      <c r="N147" s="13" t="n">
+      <c r="N148" s="16" t="n">
         <v>50</v>
       </c>
-      <c r="O147" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P147" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="18" t="inlineStr">
+      <c r="O148" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P148" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B148" s="18" t="inlineStr"/>
-      <c r="C148" s="18" t="inlineStr"/>
-      <c r="D148" s="18" t="inlineStr"/>
-      <c r="E148" s="18" t="inlineStr"/>
-      <c r="F148" s="18" t="inlineStr"/>
-      <c r="G148" s="18" t="inlineStr"/>
-      <c r="H148" s="18" t="inlineStr"/>
-      <c r="I148" s="18" t="inlineStr"/>
-      <c r="J148" s="18" t="inlineStr"/>
-      <c r="K148" s="18" t="inlineStr"/>
-      <c r="L148" s="18" t="inlineStr"/>
-      <c r="M148" s="18" t="inlineStr"/>
-      <c r="N148" s="19" t="n">
-        <v>68470.25999999999</v>
-      </c>
-      <c r="O148" s="19" t="n">
-        <v>10282.88</v>
-      </c>
-      <c r="P148" s="19" t="n">
-        <v>95.45</v>
+      <c r="B149" s="18" t="inlineStr"/>
+      <c r="C149" s="18" t="inlineStr"/>
+      <c r="D149" s="18" t="inlineStr"/>
+      <c r="E149" s="18" t="inlineStr"/>
+      <c r="F149" s="18" t="inlineStr"/>
+      <c r="G149" s="18" t="inlineStr"/>
+      <c r="H149" s="18" t="inlineStr"/>
+      <c r="I149" s="18" t="inlineStr"/>
+      <c r="J149" s="18" t="inlineStr"/>
+      <c r="K149" s="18" t="inlineStr"/>
+      <c r="L149" s="18" t="inlineStr"/>
+      <c r="M149" s="18" t="inlineStr"/>
+      <c r="N149" s="19" t="n">
+        <v>68732.95999999999</v>
+      </c>
+      <c r="O149" s="19" t="n">
+        <v>10732.88</v>
+      </c>
+      <c r="P149" s="19" t="n">
+        <v>91.17</v>
       </c>
     </row>
   </sheetData>
@@ -11286,6 +11356,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId141"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A147" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId144"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11860,26 +11931,26 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>56</v>
+        <v>64.5</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>20.25</v>
+        <v>21.5</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>0.75</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>77</v>
+        <v>86.75</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>17.75</v>
+        <v>19.75</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>486.15</v>
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>17.8%</t>
         </is>
       </c>
     </row>
@@ -11921,7 +11992,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>40.75</v>
+        <v>46.92</v>
       </c>
     </row>
   </sheetData>
@@ -12006,22 +12077,22 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>407345</v>
+        <v>406895</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>209560</v>
+        <v>207091</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>197785</v>
+        <v>199805</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>163918</v>
+        <v>160398</v>
       </c>
       <c r="F5" s="25" t="n">
-        <v>18728</v>
+        <v>24017</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>15139</v>
+        <v>15389</v>
       </c>
     </row>
     <row r="6">
@@ -12034,19 +12105,19 @@
         <v>185691</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>80558</v>
+        <v>78539</v>
       </c>
       <c r="D6" s="26" t="n">
-        <v>105133</v>
+        <v>107152</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>96374</v>
+        <v>92854</v>
       </c>
       <c r="F6" s="26" t="n">
-        <v>4770</v>
+        <v>10060</v>
       </c>
       <c r="G6" s="26" t="n">
-        <v>3988</v>
+        <v>4238</v>
       </c>
     </row>
     <row r="7">
@@ -12056,10 +12127,10 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>221654</v>
+        <v>221204</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>129002</v>
+        <v>128552</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>92652</v>
@@ -12460,7 +12531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -12481,7 +12552,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>3 clôture(s) : 3 projet(s), 0 rework</t>
+          <t>4 clôture(s) : 4 projet(s), 0 rework</t>
         </is>
       </c>
     </row>
@@ -12551,22 +12622,22 @@
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
@@ -12581,59 +12652,89 @@
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
+          <t>PDMDEP-31947</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
           <t>PDMDEP-33720</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>[COMMUNE DE LEVALLOIS PERRET] - PRESTA PURGE DES ACTES EN UR</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="n">
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>TOTAL projets clôturés</t>
         </is>
       </c>
-      <c r="B9" s="18" t="n"/>
-      <c r="C9" s="18" t="n"/>
-      <c r="D9" s="18" t="n"/>
-      <c r="E9" s="18" t="n"/>
-      <c r="F9" s="18" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="28" t="inlineStr">
+      <c r="B10" s="18" t="n"/>
+      <c r="C10" s="18" t="n"/>
+      <c r="D10" s="18" t="n"/>
+      <c r="E10" s="18" t="n"/>
+      <c r="F10" s="18" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>TOTAL rework clôturés</t>
         </is>
       </c>
-      <c r="B10" s="28" t="n"/>
-      <c r="C10" s="28" t="n"/>
-      <c r="D10" s="28" t="n"/>
-      <c r="E10" s="28" t="n"/>
-      <c r="F10" s="28" t="n">
+      <c r="B11" s="28" t="n"/>
+      <c r="C11" s="28" t="n"/>
+      <c r="D11" s="28" t="n"/>
+      <c r="E11" s="28" t="n"/>
+      <c r="F11" s="28" t="n">
         <v>0</v>
       </c>
     </row>

--- a/jira_export_2026-07-08.xlsx
+++ b/jira_export_2026-07-08.xlsx
@@ -729,7 +729,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>10,733 €</t>
+          <t>11,100 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -743,7 +743,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -776,7 +776,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>8,314 €</t>
+          <t>8,681 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -824,7 +824,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>193 h</t>
+          <t>219 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -838,7 +838,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>91.2%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -942,7 +942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P149"/>
+  <dimension ref="A1:P152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1814,7 +1814,7 @@
         <v>1</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L15" s="12" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>3207.7</v>
       </c>
       <c r="P15" s="13" t="n">
-        <v>1603.85</v>
+        <v>1069.23</v>
       </c>
     </row>
     <row r="16">
@@ -2318,7 +2318,7 @@
         <v>1</v>
       </c>
       <c r="K22" s="15" t="n">
-        <v>2.25</v>
+        <v>3.75</v>
       </c>
       <c r="L22" s="15" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>248.58</v>
       </c>
       <c r="P22" s="16" t="n">
-        <v>110.48</v>
+        <v>66.29000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -2462,7 +2462,7 @@
         <v>1</v>
       </c>
       <c r="K24" s="15" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="L24" s="15" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>2</v>
       </c>
       <c r="K38" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L38" s="15" t="inlineStr">
         <is>
@@ -4567,12 +4567,12 @@
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32848</t>
+          <t>PDMDEP-32902</t>
         </is>
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GRENOBLE] - Modification modèles de facture</t>
+          <t xml:space="preserve">[COMMUNE DE BALARUC-LES-BAINS ] - COMMANDE PAX </t>
         </is>
       </c>
       <c r="C54" s="15" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="D54" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE GRENOBLE</t>
+          <t xml:space="preserve">COMMUNE DE BALARUCL-LES-BAINS </t>
         </is>
       </c>
       <c r="E54" s="15" t="inlineStr">
         <is>
-          <t>Modification modèles de facture</t>
+          <t xml:space="preserve">COMMANDE PAX </t>
         </is>
       </c>
       <c r="F54" s="15" t="inlineStr">
@@ -4607,29 +4607,29 @@
       </c>
       <c r="I54" s="15" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="J54" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K54" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L54" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32852</t>
+          <t>PDMDEP-32910</t>
         </is>
       </c>
       <c r="M54" s="15" t="inlineStr">
         <is>
-          <t>00164564</t>
+          <t>00159637</t>
         </is>
       </c>
       <c r="N54" s="16" t="n">
-        <v>300</v>
-      </c>
-      <c r="O54" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P54" s="16" t="n">
@@ -4639,12 +4639,12 @@
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32831</t>
+          <t>PDMDEP-32848</t>
         </is>
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE PANTIN] - Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
+          <t>[COMMUNE DE GRENOBLE] - Modification modèles de facture</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE PANTIN</t>
+          <t>COMMUNE DE GRENOBLE</t>
         </is>
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
+          <t>Modification modèles de facture</t>
         </is>
       </c>
       <c r="F55" s="12" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="I55" s="12" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="J55" s="12" t="n">
@@ -4690,16 +4690,16 @@
       </c>
       <c r="L55" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32837</t>
+          <t>PDMDEP-32852</t>
         </is>
       </c>
       <c r="M55" s="12" t="inlineStr">
         <is>
-          <t>00164275</t>
+          <t>00164564</t>
         </is>
       </c>
       <c r="N55" s="13" t="n">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="O55" s="17" t="n">
         <v>0</v>
@@ -4711,32 +4711,32 @@
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-32831</t>
         </is>
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[COMMUNE DE PANTIN] - Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
         </is>
       </c>
       <c r="C56" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D56" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>COMMUNE DE PANTIN</t>
         </is>
       </c>
       <c r="E56" s="15" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
         </is>
       </c>
       <c r="F56" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G56" s="15" t="inlineStr">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="I56" s="15" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="J56" s="15" t="n">
@@ -4762,16 +4762,16 @@
       </c>
       <c r="L56" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-32837</t>
         </is>
       </c>
       <c r="M56" s="15" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00164275</t>
         </is>
       </c>
       <c r="N56" s="16" t="n">
-        <v>705</v>
+        <v>900</v>
       </c>
       <c r="O56" s="17" t="n">
         <v>0</v>
@@ -4783,12 +4783,12 @@
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32759</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE DU GRAND REIMS - DSIT] - MV app/ infra + màj carto</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE DU GRAND REIMS - DSIT</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E57" s="12" t="inlineStr">
@@ -4834,16 +4834,16 @@
       </c>
       <c r="L57" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32763</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M57" s="12" t="inlineStr">
         <is>
-          <t>00163805</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N57" s="13" t="n">
-        <v>564</v>
+        <v>705</v>
       </c>
       <c r="O57" s="17" t="n">
         <v>0</v>
@@ -4855,32 +4855,32 @@
     <row r="58">
       <c r="A58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32732</t>
+          <t>PDMDEP-32759</t>
         </is>
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
+          <t>[COMMUNAUTE URBAINE DU GRAND REIMS - DSIT] - MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="C58" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D58" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE LA SENTINELLE</t>
+          <t>COMMUNAUTE URBAINE DU GRAND REIMS - DSIT</t>
         </is>
       </c>
       <c r="E58" s="15" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Caisse</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F58" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G58" s="15" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="H58" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I58" s="15" t="inlineStr">
@@ -4902,37 +4902,37 @@
         <v>3</v>
       </c>
       <c r="K58" s="15" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="L58" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32741</t>
+          <t>PDMDEP-32763</t>
         </is>
       </c>
       <c r="M58" s="15" t="inlineStr">
         <is>
-          <t>00163789</t>
+          <t>00163805</t>
         </is>
       </c>
       <c r="N58" s="16" t="n">
-        <v>2138.2</v>
+        <v>564</v>
       </c>
       <c r="O58" s="17" t="n">
-        <v>1375.2</v>
+        <v>0</v>
       </c>
       <c r="P58" s="16" t="n">
-        <v>305.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32703</t>
+          <t>PDMDEP-32732</t>
         </is>
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[MAIRIE DE MIRIBEL] - MIGRATION PLACIER SIMPLE + PAX </t>
+          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
@@ -4942,12 +4942,12 @@
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE MIRIBEL</t>
+          <t>MAIRIE DE LA SENTINELLE</t>
         </is>
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION PLACIER SIMPLE + PAX </t>
+          <t>Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="F59" s="12" t="inlineStr">
@@ -4962,69 +4962,69 @@
       </c>
       <c r="H59" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I59" s="12" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J59" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="L59" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32712</t>
+          <t>PDMDEP-32741</t>
         </is>
       </c>
       <c r="M59" s="12" t="inlineStr">
         <is>
-          <t>00163498</t>
+          <t>00163789</t>
         </is>
       </c>
       <c r="N59" s="13" t="n">
-        <v>283.5</v>
+        <v>2138.2</v>
       </c>
       <c r="O59" s="17" t="n">
-        <v>0</v>
+        <v>1375.2</v>
       </c>
       <c r="P59" s="13" t="n">
-        <v>0</v>
+        <v>305.6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32703</t>
         </is>
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t xml:space="preserve">[MAIRIE DE MIRIBEL] - MIGRATION PLACIER SIMPLE + PAX </t>
         </is>
       </c>
       <c r="C60" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>MAIRIE DE MIRIBEL</t>
         </is>
       </c>
       <c r="E60" s="15" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t xml:space="preserve">MIGRATION PLACIER SIMPLE + PAX </t>
         </is>
       </c>
       <c r="F60" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G60" s="15" t="inlineStr">
@@ -5034,32 +5034,32 @@
       </c>
       <c r="H60" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I60" s="15" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="J60" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K60" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L60" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32712</t>
         </is>
       </c>
       <c r="M60" s="15" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00163498</t>
         </is>
       </c>
       <c r="N60" s="16" t="n">
-        <v>548.4</v>
+        <v>283.5</v>
       </c>
       <c r="O60" s="17" t="n">
         <v>0</v>
@@ -5071,32 +5071,32 @@
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32598</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Déploiement GeoDP Caisse</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G61" s="12" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="H61" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I61" s="12" t="inlineStr">
@@ -5118,20 +5118,20 @@
         <v>3</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32607</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M61" s="12" t="inlineStr">
         <is>
-          <t>00163155</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N61" s="13" t="n">
-        <v>552</v>
+        <v>548.4</v>
       </c>
       <c r="O61" s="17" t="n">
         <v>0</v>
@@ -5143,32 +5143,32 @@
     <row r="62">
       <c r="A62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32598</t>
         </is>
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="C62" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D62" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
         </is>
       </c>
       <c r="E62" s="15" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="F62" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G62" s="15" t="inlineStr">
@@ -5178,32 +5178,32 @@
       </c>
       <c r="H62" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I62" s="15" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J62" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K62" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L62" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32607</t>
         </is>
       </c>
       <c r="M62" s="15" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00163155</t>
         </is>
       </c>
       <c r="N62" s="16" t="n">
-        <v>142.1</v>
+        <v>552</v>
       </c>
       <c r="O62" s="17" t="n">
         <v>0</v>
@@ -5215,32 +5215,32 @@
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F63" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G63" s="12" t="inlineStr">
@@ -5250,32 +5250,32 @@
       </c>
       <c r="H63" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I63" s="12" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J63" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="L63" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M63" s="12" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N63" s="13" t="n">
-        <v>1868</v>
+        <v>142.1</v>
       </c>
       <c r="O63" s="17" t="n">
         <v>0</v>
@@ -5287,32 +5287,32 @@
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32442</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod </t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E64" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F64" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G64" s="15" t="inlineStr">
@@ -5322,32 +5322,32 @@
       </c>
       <c r="H64" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I64" s="15" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J64" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K64" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L64" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32446</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M64" s="15" t="inlineStr">
         <is>
-          <t>00161842</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N64" s="16" t="n">
-        <v>882.5</v>
+        <v>1868</v>
       </c>
       <c r="O64" s="17" t="n">
         <v>0</v>
@@ -5359,27 +5359,27 @@
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32400</t>
+          <t>PDMDEP-32442</t>
         </is>
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t xml:space="preserve">[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="F65" s="12" t="inlineStr">
@@ -5399,29 +5399,29 @@
       </c>
       <c r="I65" s="12" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="J65" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L65" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32406</t>
+          <t>PDMDEP-32446</t>
         </is>
       </c>
       <c r="M65" s="12" t="inlineStr">
         <is>
-          <t>00161680</t>
+          <t>00161842</t>
         </is>
       </c>
       <c r="N65" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" s="13" t="n">
+        <v>882.5</v>
+      </c>
+      <c r="O65" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P65" s="13" t="n">
@@ -5431,32 +5431,32 @@
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32400</t>
         </is>
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
         </is>
       </c>
       <c r="E66" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="F66" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G66" s="15" t="inlineStr">
@@ -5466,35 +5466,35 @@
       </c>
       <c r="H66" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I66" s="15" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="J66" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K66" s="15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L66" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32406</t>
         </is>
       </c>
       <c r="M66" s="15" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161680</t>
         </is>
       </c>
       <c r="N66" s="16" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="O66" s="16" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="P66" s="16" t="n">
         <v>0</v>
@@ -5503,32 +5503,32 @@
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F67" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G67" s="12" t="inlineStr">
@@ -5538,69 +5538,69 @@
       </c>
       <c r="H67" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I67" s="12" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J67" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L67" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M67" s="12" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N67" s="13" t="n">
-        <v>1046.5</v>
-      </c>
-      <c r="O67" s="17" t="n">
-        <v>455</v>
+        <v>450</v>
+      </c>
+      <c r="O67" s="13" t="n">
+        <v>450</v>
       </c>
       <c r="P67" s="13" t="n">
-        <v>75.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32152</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAVAILLON</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E68" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F68" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G68" s="15" t="inlineStr">
@@ -5610,64 +5610,64 @@
       </c>
       <c r="H68" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I68" s="15" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J68" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K68" s="15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L68" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32161</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M68" s="15" t="inlineStr">
         <is>
-          <t>00160661</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N68" s="16" t="n">
-        <v>765</v>
+        <v>1046.5</v>
       </c>
       <c r="O68" s="17" t="n">
-        <v>0</v>
+        <v>455</v>
       </c>
       <c r="P68" s="16" t="n">
-        <v>0</v>
+        <v>75.83</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32152</t>
         </is>
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
+          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>COMMUNE DE CAVAILLON</t>
         </is>
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr">
@@ -5694,22 +5694,22 @@
         <v>4</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L69" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32161</t>
         </is>
       </c>
       <c r="M69" s="12" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00160661</t>
         </is>
       </c>
       <c r="N69" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" s="13" t="n">
+        <v>765</v>
+      </c>
+      <c r="O69" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P69" s="13" t="n">
@@ -5719,27 +5719,27 @@
     <row r="70">
       <c r="A70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E70" s="15" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F70" s="15" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H70" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I70" s="15" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J70" s="15" t="n">
@@ -5770,18 +5770,18 @@
       </c>
       <c r="L70" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M70" s="15" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N70" s="16" t="n">
-        <v>407</v>
-      </c>
-      <c r="O70" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P70" s="16" t="n">
@@ -5791,12 +5791,12 @@
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F71" s="12" t="inlineStr">
@@ -5826,32 +5826,32 @@
       </c>
       <c r="H71" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I71" s="12" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J71" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L71" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M71" s="12" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N71" s="13" t="n">
-        <v>257.15</v>
+        <v>407</v>
       </c>
       <c r="O71" s="17" t="n">
         <v>0</v>
@@ -5863,32 +5863,32 @@
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F72" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G72" s="15" t="inlineStr">
@@ -5898,32 +5898,32 @@
       </c>
       <c r="H72" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I72" s="15" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J72" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K72" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L72" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M72" s="15" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N72" s="16" t="n">
-        <v>440.38</v>
+        <v>257.15</v>
       </c>
       <c r="O72" s="17" t="n">
         <v>0</v>
@@ -5935,32 +5935,32 @@
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G73" s="12" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="H73" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I73" s="12" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J73" s="12" t="n">
@@ -5986,16 +5986,16 @@
       </c>
       <c r="L73" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M73" s="12" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N73" s="13" t="n">
-        <v>285</v>
+        <v>440.38</v>
       </c>
       <c r="O73" s="17" t="n">
         <v>0</v>
@@ -6007,32 +6007,32 @@
     <row r="74">
       <c r="A74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G74" s="15" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="I74" s="15" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J74" s="15" t="n">
@@ -6058,16 +6058,16 @@
       </c>
       <c r="L74" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M74" s="15" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N74" s="16" t="n">
-        <v>1325</v>
+        <v>285</v>
       </c>
       <c r="O74" s="17" t="n">
         <v>0</v>
@@ -6079,12 +6079,12 @@
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="I75" s="12" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J75" s="12" t="n">
@@ -6130,19 +6130,19 @@
       </c>
       <c r="L75" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M75" s="12" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N75" s="13" t="n">
-        <v>120</v>
-      </c>
-      <c r="O75" s="13" t="n">
-        <v>120</v>
+        <v>1325</v>
+      </c>
+      <c r="O75" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P75" s="13" t="n">
         <v>0</v>
@@ -6151,32 +6151,32 @@
     <row r="76">
       <c r="A76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31938</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON- GeODP tous modules - intégration en masse n° tiers</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t>GeODP tous modules - intégration en masse n° tiers</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G76" s="15" t="inlineStr">
@@ -6202,19 +6202,19 @@
       </c>
       <c r="L76" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31942</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M76" s="15" t="inlineStr">
         <is>
-          <t>00159717</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N76" s="16" t="n">
-        <v>45</v>
-      </c>
-      <c r="O76" s="17" t="n">
-        <v>0</v>
+        <v>120</v>
+      </c>
+      <c r="O76" s="16" t="n">
+        <v>120</v>
       </c>
       <c r="P76" s="16" t="n">
         <v>0</v>
@@ -6223,27 +6223,27 @@
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31812</t>
+          <t>PDMDEP-31938</t>
         </is>
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+          <t>METROPOLE TOULON- GeODP tous modules - intégration en masse n° tiers</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE PROVINS</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>GeODP tous modules - intégration en masse n° tiers</t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="H77" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I77" s="12" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J77" s="12" t="n">
@@ -6274,16 +6274,16 @@
       </c>
       <c r="L77" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31821</t>
+          <t>PDMDEP-31942</t>
         </is>
       </c>
       <c r="M77" s="12" t="inlineStr">
         <is>
-          <t>00159471</t>
+          <t>00159717</t>
         </is>
       </c>
       <c r="N77" s="13" t="n">
-        <v>420</v>
+        <v>45</v>
       </c>
       <c r="O77" s="17" t="n">
         <v>0</v>
@@ -6295,27 +6295,27 @@
     <row r="78">
       <c r="A78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E78" s="15" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F78" s="15" t="inlineStr">
@@ -6330,35 +6330,35 @@
       </c>
       <c r="H78" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I78" s="15" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J78" s="15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K78" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L78" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M78" s="15" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N78" s="16" t="n">
-        <v>203.5</v>
-      </c>
-      <c r="O78" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O78" s="16" t="n">
+        <v>367.5</v>
       </c>
       <c r="P78" s="16" t="n">
         <v>0</v>
@@ -6367,32 +6367,32 @@
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31812</t>
         </is>
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE PROVINS</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G79" s="12" t="inlineStr">
@@ -6402,98 +6402,106 @@
       </c>
       <c r="H79" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I79" s="12" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="J79" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L79" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31821</t>
         </is>
       </c>
       <c r="M79" s="12" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00159471</t>
         </is>
       </c>
       <c r="N79" s="13" t="n">
-        <v>1500</v>
+        <v>420</v>
       </c>
       <c r="O79" s="17" t="n">
-        <v>214.9</v>
+        <v>0</v>
       </c>
       <c r="P79" s="13" t="n">
-        <v>143.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31516</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>[VIRE NORMANDIE] - Litteralis Verif</t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D80" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIRE NORMANDIE</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E80" s="15" t="inlineStr">
         <is>
-          <t>Litteralis Verif</t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F80" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G80" s="15" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H80" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I80" s="15" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J80" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K80" s="15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L80" s="15" t="inlineStr"/>
-      <c r="M80" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L80" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-31658</t>
+        </is>
+      </c>
+      <c r="M80" s="15" t="inlineStr">
+        <is>
+          <t>00158175</t>
+        </is>
+      </c>
       <c r="N80" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" s="16" t="n">
+        <v>203.5</v>
+      </c>
+      <c r="O80" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P80" s="16" t="n">
@@ -6503,32 +6511,32 @@
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31479</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 [RETOUR COMMERCE SANS REPONSE DU CLIENT]</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE TREGUIER</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G81" s="12" t="inlineStr">
@@ -6538,49 +6546,49 @@
       </c>
       <c r="H81" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I81" s="12" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J81" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="L81" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31488</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M81" s="12" t="inlineStr">
         <is>
-          <t>00157472</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N81" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" s="13" t="n">
-        <v>0</v>
+        <v>1500</v>
+      </c>
+      <c r="O81" s="17" t="n">
+        <v>214.9</v>
       </c>
       <c r="P81" s="13" t="n">
-        <v>0</v>
+        <v>143.27</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31516</t>
         </is>
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t>[VIRE NORMANDIE] - Litteralis Verif</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
@@ -6590,12 +6598,12 @@
       </c>
       <c r="D82" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE DE VIRE NORMANDIE</t>
         </is>
       </c>
       <c r="E82" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t>Litteralis Verif</t>
         </is>
       </c>
       <c r="F82" s="15" t="inlineStr">
@@ -6605,7 +6613,7 @@
       </c>
       <c r="G82" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H82" s="15" t="inlineStr">
@@ -6615,25 +6623,17 @@
       </c>
       <c r="I82" s="15" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J82" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K82" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L82" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-31468</t>
-        </is>
-      </c>
-      <c r="M82" s="15" t="inlineStr">
-        <is>
-          <t>00157346</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L82" s="15" t="inlineStr"/>
+      <c r="M82" s="15" t="inlineStr"/>
       <c r="N82" s="16" t="n">
         <v>0</v>
       </c>
@@ -6647,12 +6647,12 @@
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31479</t>
         </is>
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 [RETOUR COMMERCE SANS REPONSE DU CLIENT]</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
@@ -6662,7 +6662,7 @@
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE DE TREGUIER</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
@@ -6687,29 +6687,29 @@
       </c>
       <c r="I83" s="12" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="J83" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L83" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31488</t>
         </is>
       </c>
       <c r="M83" s="12" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157472</t>
         </is>
       </c>
       <c r="N83" s="13" t="n">
-        <v>210</v>
-      </c>
-      <c r="O83" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P83" s="13" t="n">
@@ -6719,32 +6719,32 @@
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31340</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE DINARD] - Ajout module caisse parking / Ajout export finance pour module placier </t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>Flavie BARDIN</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D84" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE DINARD</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E84" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout module caisse parking / Ajout export finance pour module placier </t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F84" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G84" s="15" t="inlineStr">
@@ -6759,23 +6759,23 @@
       </c>
       <c r="I84" s="15" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J84" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K84" s="15" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L84" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31346</t>
+          <t>PDMDEP-31468</t>
         </is>
       </c>
       <c r="M84" s="15" t="inlineStr">
         <is>
-          <t>00157037</t>
+          <t>00157346</t>
         </is>
       </c>
       <c r="N84" s="16" t="n">
@@ -6791,32 +6791,32 @@
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31285</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LUNEL] - FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>Valentin CAUJOLLE</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LUNEL</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F85" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G85" s="12" t="inlineStr">
@@ -6826,12 +6826,12 @@
       </c>
       <c r="H85" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I85" s="12" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J85" s="12" t="n">
@@ -6842,16 +6842,16 @@
       </c>
       <c r="L85" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31289</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M85" s="12" t="inlineStr">
         <is>
-          <t>00156834</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N85" s="13" t="n">
-        <v>71.2</v>
+        <v>210</v>
       </c>
       <c r="O85" s="17" t="n">
         <v>0</v>
@@ -6863,32 +6863,32 @@
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31269</t>
+          <t>PDMDEP-31340</t>
         </is>
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - Crédit d'heures</t>
+          <t xml:space="preserve">[COMMUNE DE DINARD] - Ajout module caisse parking / Ajout export finance pour module placier </t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Flavie BARDIN</t>
         </is>
       </c>
       <c r="D86" s="15" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>COMMUNE DE DINARD</t>
         </is>
       </c>
       <c r="E86" s="15" t="inlineStr">
         <is>
-          <t>Crédit d'heures</t>
+          <t xml:space="preserve">Ajout module caisse parking / Ajout export finance pour module placier </t>
         </is>
       </c>
       <c r="F86" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G86" s="15" t="inlineStr">
@@ -6903,23 +6903,23 @@
       </c>
       <c r="I86" s="15" t="inlineStr">
         <is>
-          <t>13/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J86" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K86" s="15" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L86" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31273</t>
+          <t>PDMDEP-31346</t>
         </is>
       </c>
       <c r="M86" s="15" t="inlineStr">
         <is>
-          <t>0000ENATTENTEVRAIBDC</t>
+          <t>00157037</t>
         </is>
       </c>
       <c r="N86" s="16" t="n">
@@ -6935,32 +6935,32 @@
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31285</t>
         </is>
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LUNEL] - FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Valentin CAUJOLLE</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LUNEL</t>
         </is>
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
         </is>
       </c>
       <c r="F87" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G87" s="12" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="H87" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I87" s="12" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>16/02/2026</t>
         </is>
       </c>
       <c r="J87" s="12" t="n">
@@ -6986,16 +6986,16 @@
       </c>
       <c r="L87" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31289</t>
         </is>
       </c>
       <c r="M87" s="12" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00156834</t>
         </is>
       </c>
       <c r="N87" s="13" t="n">
-        <v>130</v>
+        <v>71.2</v>
       </c>
       <c r="O87" s="17" t="n">
         <v>0</v>
@@ -7007,32 +7007,32 @@
     <row r="88">
       <c r="A88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31269</t>
         </is>
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[DIJON METROPOLE] - Crédit d'heures</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D88" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E88" s="15" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Crédit d'heures</t>
         </is>
       </c>
       <c r="F88" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G88" s="15" t="inlineStr">
@@ -7042,34 +7042,34 @@
       </c>
       <c r="H88" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I88" s="15" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>13/02/2026</t>
         </is>
       </c>
       <c r="J88" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K88" s="15" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L88" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31273</t>
         </is>
       </c>
       <c r="M88" s="15" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>0000ENATTENTEVRAIBDC</t>
         </is>
       </c>
       <c r="N88" s="16" t="n">
-        <v>255</v>
-      </c>
-      <c r="O88" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P88" s="16" t="n">
@@ -7079,12 +7079,12 @@
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30358</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARGELES-SUR-MER</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F89" s="12" t="inlineStr">
@@ -7119,27 +7119,27 @@
       </c>
       <c r="I89" s="12" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J89" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K89" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L89" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30366</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M89" s="12" t="inlineStr">
         <is>
-          <t>00154569</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N89" s="13" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="O89" s="17" t="n">
         <v>0</v>
@@ -7151,12 +7151,12 @@
     <row r="90">
       <c r="A90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
@@ -7166,12 +7166,12 @@
       </c>
       <c r="D90" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E90" s="15" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F90" s="15" t="inlineStr">
@@ -7191,27 +7191,27 @@
       </c>
       <c r="I90" s="15" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J90" s="15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K90" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L90" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M90" s="15" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N90" s="16" t="n">
-        <v>140</v>
+        <v>255</v>
       </c>
       <c r="O90" s="17" t="n">
         <v>0</v>
@@ -7223,27 +7223,27 @@
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30311</t>
+          <t>PDMDEP-30358</t>
         </is>
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CAEN] - GeODP - Modification des marges via activation Editique</t>
+          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAEN</t>
+          <t>COMMUNE D'ARGELES-SUR-MER</t>
         </is>
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>GeODP - Modification des marges via activation Editique</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F91" s="12" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="I91" s="12" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="J91" s="12" t="n">
@@ -7274,16 +7274,16 @@
       </c>
       <c r="L91" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30316</t>
+          <t>PDMDEP-30366</t>
         </is>
       </c>
       <c r="M91" s="12" t="inlineStr">
         <is>
-          <t>00154362</t>
+          <t>00154569</t>
         </is>
       </c>
       <c r="N91" s="13" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="O91" s="17" t="n">
         <v>0</v>
@@ -7295,32 +7295,32 @@
     <row r="92">
       <c r="A92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D92" s="15" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E92" s="15" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F92" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G92" s="15" t="inlineStr">
@@ -7330,34 +7330,34 @@
       </c>
       <c r="H92" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I92" s="15" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J92" s="15" t="n">
         <v>6</v>
       </c>
       <c r="K92" s="15" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L92" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M92" s="15" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N92" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O92" s="16" t="n">
+        <v>140</v>
+      </c>
+      <c r="O92" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P92" s="16" t="n">
@@ -7367,32 +7367,32 @@
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30062</t>
+          <t>PDMDEP-30311</t>
         </is>
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
+          <t>[COMMUNE DE CAEN] - GeODP - Modification des marges via activation Editique</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>Commune de Saint-Dizier</t>
+          <t>COMMUNE DE CAEN</t>
         </is>
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
+          <t>GeODP - Modification des marges via activation Editique</t>
         </is>
       </c>
       <c r="F93" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G93" s="12" t="inlineStr">
@@ -7402,32 +7402,32 @@
       </c>
       <c r="H93" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I93" s="12" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>27/01/2026</t>
         </is>
       </c>
       <c r="J93" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K93" s="12" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L93" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30063</t>
+          <t>PDMDEP-30316</t>
         </is>
       </c>
       <c r="M93" s="12" t="inlineStr">
         <is>
-          <t>00153633</t>
+          <t>00154362</t>
         </is>
       </c>
       <c r="N93" s="13" t="n">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="O93" s="17" t="n">
         <v>0</v>
@@ -7439,27 +7439,27 @@
     <row r="94">
       <c r="A94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D94" s="15" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E94" s="15" t="inlineStr">
         <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F94" s="15" t="inlineStr">
@@ -7479,23 +7479,23 @@
       </c>
       <c r="I94" s="15" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J94" s="15" t="n">
         <v>6</v>
       </c>
       <c r="K94" s="15" t="n">
-        <v>4</v>
+        <v>0.75</v>
       </c>
       <c r="L94" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M94" s="15" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N94" s="16" t="n">
@@ -7511,27 +7511,27 @@
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30062</t>
         </is>
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>Commune de Saint-Dizier</t>
         </is>
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
         </is>
       </c>
       <c r="F95" s="12" t="inlineStr">
@@ -7551,29 +7551,29 @@
       </c>
       <c r="I95" s="12" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="J95" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K95" s="12" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L95" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-30063</t>
         </is>
       </c>
       <c r="M95" s="12" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00153633</t>
         </is>
       </c>
       <c r="N95" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O95" s="13" t="n">
+        <v>350</v>
+      </c>
+      <c r="O95" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P95" s="13" t="n">
@@ -7583,12 +7583,12 @@
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
@@ -7598,12 +7598,12 @@
       </c>
       <c r="D96" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>MAIRE DE PONTARLIER</t>
         </is>
       </c>
       <c r="E96" s="15" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
         </is>
       </c>
       <c r="F96" s="15" t="inlineStr">
@@ -7623,23 +7623,23 @@
       </c>
       <c r="I96" s="15" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J96" s="15" t="n">
         <v>6</v>
       </c>
       <c r="K96" s="15" t="n">
-        <v>0.25</v>
+        <v>6</v>
       </c>
       <c r="L96" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M96" s="15" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N96" s="16" t="n">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L97" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M97" s="12" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N97" s="13" t="n">
@@ -7727,26 +7727,28 @@
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29122</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES DEUX SEVRES (CD 79) - LITTERALIS - Flux WFS communication</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES DEUX SEVRES (CD 79)</t>
-        </is>
-      </c>
-      <c r="E98" s="15" t="n">
-        <v/>
+          <t>COMMUNE DE BIARRITZ</t>
+        </is>
+      </c>
+      <c r="E98" s="15" t="inlineStr">
+        <is>
+          <t>Paramétrages complémentaires + Vision</t>
+        </is>
       </c>
       <c r="F98" s="15" t="inlineStr">
         <is>
@@ -7765,29 +7767,29 @@
       </c>
       <c r="I98" s="15" t="inlineStr">
         <is>
-          <t>19/12/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J98" s="15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K98" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L98" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29124</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M98" s="15" t="inlineStr">
         <is>
-          <t>00148148</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N98" s="16" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="O98" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P98" s="16" t="n">
@@ -7797,26 +7799,28 @@
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E99" s="12" t="n">
-        <v/>
+          <t>COMMUNE DE BIARRITZ</t>
+        </is>
+      </c>
+      <c r="E99" s="12" t="inlineStr">
+        <is>
+          <t>Paramétrages complémentaires + Vision</t>
+        </is>
       </c>
       <c r="F99" s="12" t="inlineStr">
         <is>
@@ -7830,34 +7834,34 @@
       </c>
       <c r="H99" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I99" s="12" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J99" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K99" s="12" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L99" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M99" s="12" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N99" s="13" t="n">
-        <v>2812.32</v>
-      </c>
-      <c r="O99" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P99" s="13" t="n">
@@ -7867,12 +7871,12 @@
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-29122</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>DEPARTEMENT DES DEUX SEVRES (CD 79) - LITTERALIS - Flux WFS communication</t>
         </is>
       </c>
       <c r="C100" s="15" t="inlineStr">
@@ -7882,13 +7886,11 @@
       </c>
       <c r="D100" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E100" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>DEPARTEMENT DES DEUX SEVRES (CD 79)</t>
+        </is>
+      </c>
+      <c r="E100" s="15" t="n">
+        <v/>
       </c>
       <c r="F100" s="15" t="inlineStr">
         <is>
@@ -7902,32 +7904,32 @@
       </c>
       <c r="H100" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I100" s="15" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>19/12/2025</t>
         </is>
       </c>
       <c r="J100" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K100" s="15" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L100" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-29124</t>
         </is>
       </c>
       <c r="M100" s="15" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00148148</t>
         </is>
       </c>
       <c r="N100" s="16" t="n">
-        <v>392.5</v>
+        <v>157.5</v>
       </c>
       <c r="O100" s="17" t="n">
         <v>0</v>
@@ -7939,12 +7941,12 @@
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
@@ -7954,13 +7956,11 @@
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E101" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="n">
+        <v/>
       </c>
       <c r="F101" s="12" t="inlineStr">
         <is>
@@ -7979,27 +7979,27 @@
       </c>
       <c r="I101" s="12" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J101" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K101" s="12" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="L101" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M101" s="12" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N101" s="13" t="n">
-        <v>1556.25</v>
+        <v>2812.32</v>
       </c>
       <c r="O101" s="17" t="n">
         <v>0</v>
@@ -8062,16 +8062,16 @@
       </c>
       <c r="L102" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M102" s="15" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N102" s="16" t="n">
-        <v>1790</v>
+        <v>392.5</v>
       </c>
       <c r="O102" s="17" t="n">
         <v>0</v>
@@ -8134,18 +8134,18 @@
       </c>
       <c r="L103" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M103" s="12" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N103" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O103" s="13" t="n">
+        <v>1556.25</v>
+      </c>
+      <c r="O103" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P103" s="13" t="n">
@@ -8206,18 +8206,18 @@
       </c>
       <c r="L104" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M104" s="15" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N104" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O104" s="16" t="n">
+        <v>1790</v>
+      </c>
+      <c r="O104" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P104" s="16" t="n">
@@ -8227,12 +8227,12 @@
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
@@ -8242,11 +8242,13 @@
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E105" s="12" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F105" s="12" t="inlineStr">
         <is>
@@ -8260,28 +8262,28 @@
       </c>
       <c r="H105" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I105" s="12" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J105" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K105" s="12" t="n">
-        <v>4.25</v>
+        <v>0.8</v>
       </c>
       <c r="L105" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M105" s="12" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N105" s="13" t="n">
@@ -8297,12 +8299,12 @@
     <row r="106">
       <c r="A106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C106" s="15" t="inlineStr">
@@ -8312,11 +8314,13 @@
       </c>
       <c r="D106" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
-        </is>
-      </c>
-      <c r="E106" s="15" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E106" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F106" s="15" t="inlineStr">
         <is>
@@ -8335,29 +8339,29 @@
       </c>
       <c r="I106" s="15" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J106" s="15" t="n">
         <v>8</v>
       </c>
       <c r="K106" s="15" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="L106" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M106" s="15" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N106" s="16" t="n">
-        <v>732</v>
-      </c>
-      <c r="O106" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P106" s="16" t="n">
@@ -8367,12 +8371,12 @@
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26831</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
@@ -8382,34 +8386,48 @@
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>CD74</t>
-        </is>
-      </c>
-      <c r="E107" s="12" t="inlineStr">
-        <is>
-          <t>MAJ carto</t>
-        </is>
-      </c>
-      <c r="F107" s="12" t="inlineStr"/>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
+        </is>
+      </c>
+      <c r="E107" s="12" t="n">
+        <v/>
+      </c>
+      <c r="F107" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="H107" s="12" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H107" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I107" s="12" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J107" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K107" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L107" s="12" t="inlineStr"/>
-      <c r="M107" s="12" t="inlineStr"/>
+        <v>4.25</v>
+      </c>
+      <c r="L107" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-27642</t>
+        </is>
+      </c>
+      <c r="M107" s="12" t="inlineStr">
+        <is>
+          <t>00143935</t>
+        </is>
+      </c>
       <c r="N107" s="13" t="n">
         <v>0</v>
       </c>
@@ -8423,12 +8441,12 @@
     <row r="108">
       <c r="A108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C108" s="15" t="inlineStr">
@@ -8438,7 +8456,7 @@
       </c>
       <c r="D108" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
         </is>
       </c>
       <c r="E108" s="15" t="n">
@@ -8456,34 +8474,34 @@
       </c>
       <c r="H108" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I108" s="15" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J108" s="15" t="n">
         <v>8</v>
       </c>
       <c r="K108" s="15" t="n">
-        <v>0.25</v>
+        <v>2.5</v>
       </c>
       <c r="L108" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-26814</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M108" s="15" t="inlineStr">
         <is>
-          <t>00142941</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N108" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O108" s="16" t="n">
+        <v>732</v>
+      </c>
+      <c r="O108" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P108" s="16" t="n">
@@ -8493,65 +8511,49 @@
     <row r="109">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26782</t>
+          <t>PDMDEP-26831</t>
         </is>
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
+          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
+          <t>CD74</t>
         </is>
       </c>
       <c r="E109" s="12" t="inlineStr">
         <is>
-          <t>Déploiement LiEx</t>
-        </is>
-      </c>
-      <c r="F109" s="12" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+          <t>MAJ carto</t>
+        </is>
+      </c>
+      <c r="F109" s="12" t="inlineStr"/>
       <c r="G109" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H109" s="12" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="H109" s="12" t="inlineStr"/>
       <c r="I109" s="12" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="J109" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K109" s="12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L109" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-26783</t>
-        </is>
-      </c>
-      <c r="M109" s="12" t="inlineStr">
-        <is>
-          <t>00142659</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L109" s="12" t="inlineStr"/>
+      <c r="M109" s="12" t="inlineStr"/>
       <c r="N109" s="13" t="n">
         <v>0</v>
       </c>
@@ -8565,12 +8567,12 @@
     <row r="110">
       <c r="A110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C110" s="15" t="inlineStr">
@@ -8580,7 +8582,7 @@
       </c>
       <c r="D110" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E110" s="15" t="n">
@@ -8598,34 +8600,34 @@
       </c>
       <c r="H110" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I110" s="15" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J110" s="15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K110" s="15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L110" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M110" s="15" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N110" s="16" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O110" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P110" s="16" t="n">
@@ -8635,26 +8637,28 @@
     <row r="111">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24765</t>
+          <t>PDMDEP-26782</t>
         </is>
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t>[COLOMBES] -  Litteralis - Interface Pastell</t>
+          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE COLOMBES - DSIO</t>
-        </is>
-      </c>
-      <c r="E111" s="12" t="n">
-        <v/>
+          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
+        </is>
+      </c>
+      <c r="E111" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement LiEx</t>
+        </is>
       </c>
       <c r="F111" s="12" t="inlineStr">
         <is>
@@ -8668,28 +8672,28 @@
       </c>
       <c r="H111" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I111" s="12" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="J111" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K111" s="12" t="n">
-        <v>0.5</v>
+        <v>6.75</v>
       </c>
       <c r="L111" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28062</t>
+          <t>PDMDEP-26783</t>
         </is>
       </c>
       <c r="M111" s="12" t="inlineStr">
         <is>
-          <t>500768</t>
+          <t>00142659</t>
         </is>
       </c>
       <c r="N111" s="13" t="n">
@@ -8705,22 +8709,22 @@
     <row r="112">
       <c r="A112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24426</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>[DRANCY] - Migration STD vers Exp</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C112" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D112" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE DRANCY</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E112" s="15" t="n">
@@ -8738,34 +8742,34 @@
       </c>
       <c r="H112" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I112" s="15" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J112" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K112" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L112" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27028</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M112" s="15" t="inlineStr">
         <is>
-          <t>500950</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N112" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O112" s="16" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O112" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P112" s="16" t="n">
@@ -8775,22 +8779,22 @@
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24765</t>
         </is>
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>[COLOMBES] -  Litteralis - Interface Pastell</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
+          <t>VILLE DE COLOMBES - DSIO</t>
         </is>
       </c>
       <c r="E113" s="12" t="n">
@@ -8808,28 +8812,28 @@
       </c>
       <c r="H113" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I113" s="12" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="J113" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K113" s="12" t="n">
-        <v>1.38</v>
+        <v>0.5</v>
       </c>
       <c r="L113" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27996</t>
+          <t>PDMDEP-28062</t>
         </is>
       </c>
       <c r="M113" s="12" t="inlineStr">
         <is>
-          <t>501219</t>
+          <t>500768</t>
         </is>
       </c>
       <c r="N113" s="13" t="n">
@@ -8845,12 +8849,12 @@
     <row r="114">
       <c r="A114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24426</t>
         </is>
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>[DRANCY] - Migration STD vers Exp</t>
         </is>
       </c>
       <c r="C114" s="15" t="inlineStr">
@@ -8860,7 +8864,7 @@
       </c>
       <c r="D114" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
+          <t>VILLE DE DRANCY</t>
         </is>
       </c>
       <c r="E114" s="15" t="n">
@@ -8878,28 +8882,28 @@
       </c>
       <c r="H114" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I114" s="15" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="J114" s="15" t="n">
         <v>10</v>
       </c>
       <c r="K114" s="15" t="n">
-        <v>1.38</v>
+        <v>0.25</v>
       </c>
       <c r="L114" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27995</t>
+          <t>PDMDEP-27028</t>
         </is>
       </c>
       <c r="M114" s="15" t="inlineStr">
         <is>
-          <t>501218</t>
+          <t>500950</t>
         </is>
       </c>
       <c r="N114" s="16" t="n">
@@ -8915,22 +8919,22 @@
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E115" s="12" t="n">
@@ -8953,29 +8957,29 @@
       </c>
       <c r="I115" s="12" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J115" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K115" s="12" t="n">
-        <v>2</v>
+        <v>1.38</v>
       </c>
       <c r="L115" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M115" s="12" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N115" s="13" t="n">
-        <v>2323</v>
-      </c>
-      <c r="O115" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P115" s="13" t="n">
@@ -8985,22 +8989,22 @@
     <row r="116">
       <c r="A116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23486</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON- AJOUT BALISE FILIEN</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C116" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D116" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E116" s="15" t="n">
@@ -9008,7 +9012,7 @@
       </c>
       <c r="F116" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G116" s="15" t="inlineStr">
@@ -9018,34 +9022,34 @@
       </c>
       <c r="H116" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I116" s="15" t="inlineStr">
         <is>
-          <t>25/07/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J116" s="15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K116" s="15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="L116" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27493</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M116" s="15" t="inlineStr">
         <is>
-          <t>495699</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N116" s="16" t="n">
-        <v>964.1</v>
-      </c>
-      <c r="O116" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P116" s="16" t="n">
@@ -9055,22 +9059,22 @@
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-23484</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON- AJOUT LIEU DE NAISSANCE DANS FILIEN</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E117" s="12" t="n">
@@ -9078,7 +9082,7 @@
       </c>
       <c r="F117" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G117" s="12" t="inlineStr">
@@ -9088,35 +9092,35 @@
       </c>
       <c r="H117" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I117" s="12" t="inlineStr">
         <is>
-          <t>25/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J117" s="12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K117" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L117" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27494</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M117" s="12" t="inlineStr">
         <is>
-          <t>495695</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N117" s="13" t="n">
-        <v>140.4</v>
+        <v>2323</v>
       </c>
       <c r="O117" s="17" t="n">
-        <v>70.2</v>
+        <v>0</v>
       </c>
       <c r="P117" s="13" t="n">
         <v>0</v>
@@ -9125,22 +9129,22 @@
     <row r="118">
       <c r="A118" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-23486</t>
         </is>
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>METROPOLE TOULON- AJOUT BALISE FILIEN</t>
         </is>
       </c>
       <c r="C118" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D118" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E118" s="15" t="n">
@@ -9148,7 +9152,7 @@
       </c>
       <c r="F118" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G118" s="15" t="inlineStr">
@@ -9158,34 +9162,34 @@
       </c>
       <c r="H118" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I118" s="15" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>25/07/2025</t>
         </is>
       </c>
       <c r="J118" s="15" t="n">
         <v>12</v>
       </c>
       <c r="K118" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L118" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-27493</t>
         </is>
       </c>
       <c r="M118" s="15" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>495699</t>
         </is>
       </c>
       <c r="N118" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O118" s="16" t="n">
+        <v>964.1</v>
+      </c>
+      <c r="O118" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P118" s="16" t="n">
@@ -9195,17 +9199,17 @@
     <row r="119">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-22996</t>
+          <t>PDMDEP-23484</t>
         </is>
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
+          <t>METROPOLE TOULON- AJOUT LIEU DE NAISSANCE DANS FILIEN</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
@@ -9218,7 +9222,7 @@
       </c>
       <c r="F119" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G119" s="12" t="inlineStr">
@@ -9233,30 +9237,30 @@
       </c>
       <c r="I119" s="12" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>25/07/2025</t>
         </is>
       </c>
       <c r="J119" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K119" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L119" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28051</t>
+          <t>PDMDEP-27494</t>
         </is>
       </c>
       <c r="M119" s="12" t="inlineStr">
         <is>
-          <t>487190</t>
+          <t>495695</t>
         </is>
       </c>
       <c r="N119" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O119" s="13" t="n">
-        <v>0</v>
+        <v>140.4</v>
+      </c>
+      <c r="O119" s="17" t="n">
+        <v>70.2</v>
       </c>
       <c r="P119" s="13" t="n">
         <v>0</v>
@@ -9265,12 +9269,12 @@
     <row r="120">
       <c r="A120" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C120" s="15" t="inlineStr">
@@ -9280,7 +9284,7 @@
       </c>
       <c r="D120" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E120" s="15" t="n">
@@ -9303,23 +9307,23 @@
       </c>
       <c r="I120" s="15" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J120" s="15" t="n">
         <v>12</v>
       </c>
       <c r="K120" s="15" t="n">
-        <v>0.12</v>
+        <v>1</v>
       </c>
       <c r="L120" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M120" s="15" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N120" s="16" t="n">
@@ -9335,22 +9339,22 @@
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-22996</t>
         </is>
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E121" s="12" t="n">
@@ -9368,28 +9372,28 @@
       </c>
       <c r="H121" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I121" s="12" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="J121" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K121" s="12" t="n">
-        <v>0.12</v>
+        <v>2</v>
       </c>
       <c r="L121" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-28051</t>
         </is>
       </c>
       <c r="M121" s="12" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>487190</t>
         </is>
       </c>
       <c r="N121" s="13" t="n">
@@ -9420,7 +9424,7 @@
       </c>
       <c r="D122" s="15" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E122" s="15" t="n">
@@ -9454,12 +9458,12 @@
       </c>
       <c r="L122" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M122" s="15" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N122" s="16" t="n">
@@ -9524,12 +9528,12 @@
       </c>
       <c r="L123" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M123" s="12" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N123" s="13" t="n">
@@ -9545,12 +9549,12 @@
     <row r="124">
       <c r="A124" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-22496</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B124" s="15" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - LITTERALIS Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C124" s="15" t="inlineStr">
@@ -9560,7 +9564,7 @@
       </c>
       <c r="D124" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E124" s="15" t="n">
@@ -9578,28 +9582,28 @@
       </c>
       <c r="H124" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I124" s="15" t="inlineStr">
         <is>
-          <t>23/06/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J124" s="15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K124" s="15" t="n">
-        <v>0.5</v>
+        <v>0.12</v>
       </c>
       <c r="L124" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27371</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M124" s="15" t="inlineStr">
         <is>
-          <t>481817</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N124" s="16" t="n">
@@ -9615,22 +9619,22 @@
     <row r="125">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21546</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>VILLEURBANNE</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E125" s="12" t="n">
@@ -9638,7 +9642,7 @@
       </c>
       <c r="F125" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G125" s="12" t="inlineStr">
@@ -9648,34 +9652,34 @@
       </c>
       <c r="H125" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I125" s="12" t="inlineStr">
         <is>
-          <t>05/05/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J125" s="12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K125" s="12" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="L125" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28038</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M125" s="12" t="inlineStr">
         <is>
-          <t>478867</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N125" s="13" t="n">
-        <v>482.72</v>
-      </c>
-      <c r="O125" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P125" s="13" t="n">
@@ -9685,22 +9689,22 @@
     <row r="126">
       <c r="A126" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-22496</t>
         </is>
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[VILLEJUIF] - LITTERALIS Pastell</t>
         </is>
       </c>
       <c r="C126" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D126" s="15" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E126" s="15" t="n">
@@ -9718,28 +9722,28 @@
       </c>
       <c r="H126" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I126" s="15" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>23/06/2025</t>
         </is>
       </c>
       <c r="J126" s="15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K126" s="15" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L126" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-27371</t>
         </is>
       </c>
       <c r="M126" s="15" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>481817</t>
         </is>
       </c>
       <c r="N126" s="16" t="n">
@@ -9755,22 +9759,22 @@
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E127" s="12" t="n">
@@ -9793,29 +9797,29 @@
       </c>
       <c r="I127" s="12" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J127" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K127" s="12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L127" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M127" s="12" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N127" s="13" t="n">
-        <v>250</v>
-      </c>
-      <c r="O127" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P127" s="13" t="n">
@@ -9825,22 +9829,22 @@
     <row r="128">
       <c r="A128" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21546</t>
         </is>
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
         </is>
       </c>
       <c r="C128" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D128" s="15" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>VILLEURBANNE</t>
         </is>
       </c>
       <c r="E128" s="15" t="n">
@@ -9848,7 +9852,7 @@
       </c>
       <c r="F128" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G128" s="15" t="inlineStr">
@@ -9863,27 +9867,27 @@
       </c>
       <c r="I128" s="15" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="J128" s="15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K128" s="15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L128" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28038</t>
         </is>
       </c>
       <c r="M128" s="15" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>478867</t>
         </is>
       </c>
       <c r="N128" s="16" t="n">
-        <v>230</v>
+        <v>482.72</v>
       </c>
       <c r="O128" s="17" t="n">
         <v>0</v>
@@ -9895,22 +9899,22 @@
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E129" s="12" t="n">
@@ -9926,20 +9930,32 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H129" s="12" t="inlineStr"/>
+      <c r="H129" s="12" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I129" s="12" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J129" s="12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K129" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L129" s="12" t="inlineStr"/>
-      <c r="M129" s="12" t="inlineStr"/>
+        <v>0.75</v>
+      </c>
+      <c r="L129" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28036</t>
+        </is>
+      </c>
+      <c r="M129" s="12" t="inlineStr">
+        <is>
+          <t>483799</t>
+        </is>
+      </c>
       <c r="N129" s="13" t="n">
         <v>0</v>
       </c>
@@ -9953,22 +9969,22 @@
     <row r="130">
       <c r="A130" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C130" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D130" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E130" s="15" t="n">
@@ -9991,29 +10007,29 @@
       </c>
       <c r="I130" s="15" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J130" s="15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K130" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L130" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27568</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M130" s="15" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N130" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O130" s="16" t="n">
+        <v>250</v>
+      </c>
+      <c r="O130" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P130" s="16" t="n">
@@ -10023,12 +10039,12 @@
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
@@ -10038,7 +10054,7 @@
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E131" s="12" t="n">
@@ -10056,34 +10072,34 @@
       </c>
       <c r="H131" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I131" s="12" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J131" s="12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K131" s="12" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="L131" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27377</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M131" s="12" t="inlineStr">
         <is>
-          <t>478048</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N131" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O131" s="13" t="n">
+        <v>230</v>
+      </c>
+      <c r="O131" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P131" s="13" t="n">
@@ -10093,22 +10109,22 @@
     <row r="132">
       <c r="A132" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19385</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C132" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D132" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARCUEIL</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E132" s="15" t="n">
@@ -10124,32 +10140,20 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H132" s="15" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H132" s="15" t="inlineStr"/>
       <c r="I132" s="15" t="inlineStr">
         <is>
-          <t>24/02/2025</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J132" s="15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K132" s="15" t="n">
         <v>0.25</v>
       </c>
-      <c r="L132" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-27535</t>
-        </is>
-      </c>
-      <c r="M132" s="15" t="inlineStr">
-        <is>
-          <t>465345</t>
-        </is>
-      </c>
+      <c r="L132" s="15" t="inlineStr"/>
+      <c r="M132" s="15" t="inlineStr"/>
       <c r="N132" s="16" t="n">
         <v>0</v>
       </c>
@@ -10163,12 +10167,12 @@
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
@@ -10178,7 +10182,7 @@
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E133" s="12" t="n">
@@ -10191,27 +10195,35 @@
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H133" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I133" s="12" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J133" s="12" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K133" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="L133" s="12" t="inlineStr"/>
-      <c r="M133" s="12" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L133" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-27568</t>
+        </is>
+      </c>
+      <c r="M133" s="12" t="inlineStr">
+        <is>
+          <t>471958</t>
+        </is>
+      </c>
       <c r="N133" s="13" t="n">
         <v>0</v>
       </c>
@@ -10225,22 +10237,22 @@
     <row r="134">
       <c r="A134" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B134" s="15" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C134" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D134" s="15" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
         </is>
       </c>
       <c r="E134" s="15" t="n">
@@ -10248,7 +10260,7 @@
       </c>
       <c r="F134" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G134" s="15" t="inlineStr">
@@ -10258,34 +10270,34 @@
       </c>
       <c r="H134" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I134" s="15" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J134" s="15" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K134" s="15" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L134" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-27377</t>
         </is>
       </c>
       <c r="M134" s="15" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>478048</t>
         </is>
       </c>
       <c r="N134" s="16" t="n">
-        <v>240</v>
-      </c>
-      <c r="O134" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P134" s="16" t="n">
@@ -10295,12 +10307,12 @@
     <row r="135">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-19385</t>
         </is>
       </c>
       <c r="B135" s="12" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
@@ -10310,7 +10322,7 @@
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
+          <t>COMMUNE D'ARCUEIL</t>
         </is>
       </c>
       <c r="E135" s="12" t="n">
@@ -10328,28 +10340,28 @@
       </c>
       <c r="H135" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I135" s="12" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>24/02/2025</t>
         </is>
       </c>
       <c r="J135" s="12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K135" s="12" t="n">
-        <v>0.62</v>
+        <v>0.25</v>
       </c>
       <c r="L135" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34362</t>
+          <t>PDMDEP-27535</t>
         </is>
       </c>
       <c r="M135" s="12" t="inlineStr">
         <is>
-          <t>458057</t>
+          <t>465345</t>
         </is>
       </c>
       <c r="N135" s="13" t="n">
@@ -10365,12 +10377,12 @@
     <row r="136">
       <c r="A136" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B136" s="15" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C136" s="15" t="inlineStr">
@@ -10380,7 +10392,7 @@
       </c>
       <c r="D136" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E136" s="15" t="n">
@@ -10393,35 +10405,27 @@
       </c>
       <c r="G136" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H136" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I136" s="15" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J136" s="15" t="n">
         <v>19</v>
       </c>
       <c r="K136" s="15" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="L136" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28020</t>
-        </is>
-      </c>
-      <c r="M136" s="15" t="inlineStr">
-        <is>
-          <t>458057</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="L136" s="15" t="inlineStr"/>
+      <c r="M136" s="15" t="inlineStr"/>
       <c r="N136" s="16" t="n">
         <v>0</v>
       </c>
@@ -10435,12 +10439,12 @@
     <row r="137">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-16868</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
-          <t>[Limoges] migration placier</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
@@ -10450,7 +10454,7 @@
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>Limoges</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E137" s="12" t="n">
@@ -10463,7 +10467,7 @@
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H137" s="12" t="inlineStr">
@@ -10473,21 +10477,29 @@
       </c>
       <c r="I137" s="12" t="inlineStr">
         <is>
-          <t>26/09/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J137" s="12" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K137" s="12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L137" s="12" t="inlineStr"/>
-      <c r="M137" s="12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L137" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M137" s="12" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
       <c r="N137" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O137" s="13" t="n">
+        <v>240</v>
+      </c>
+      <c r="O137" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P137" s="13" t="n">
@@ -10497,22 +10509,22 @@
     <row r="138">
       <c r="A138" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C138" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D138" s="15" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
         </is>
       </c>
       <c r="E138" s="15" t="n">
@@ -10525,7 +10537,7 @@
       </c>
       <c r="G138" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H138" s="15" t="inlineStr">
@@ -10535,17 +10547,25 @@
       </c>
       <c r="I138" s="15" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J138" s="15" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="K138" s="15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L138" s="15" t="inlineStr"/>
-      <c r="M138" s="15" t="inlineStr"/>
+        <v>0.62</v>
+      </c>
+      <c r="L138" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-34362</t>
+        </is>
+      </c>
+      <c r="M138" s="15" t="inlineStr">
+        <is>
+          <t>458057</t>
+        </is>
+      </c>
       <c r="N138" s="16" t="n">
         <v>0</v>
       </c>
@@ -10559,12 +10579,12 @@
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14551</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t>[Perpignan] Interface formulaire</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
@@ -10574,7 +10594,7 @@
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>[Perpignan]</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E139" s="12" t="n">
@@ -10587,7 +10607,7 @@
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H139" s="12" t="inlineStr">
@@ -10597,17 +10617,25 @@
       </c>
       <c r="I139" s="12" t="inlineStr">
         <is>
-          <t>14/03/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J139" s="12" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="K139" s="12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L139" s="12" t="inlineStr"/>
-      <c r="M139" s="12" t="inlineStr"/>
+        <v>0.62</v>
+      </c>
+      <c r="L139" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28020</t>
+        </is>
+      </c>
+      <c r="M139" s="12" t="inlineStr">
+        <is>
+          <t>458057</t>
+        </is>
+      </c>
       <c r="N139" s="13" t="n">
         <v>0</v>
       </c>
@@ -10621,22 +10649,22 @@
     <row r="140">
       <c r="A140" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14254</t>
+          <t>PDMDEP-16868</t>
         </is>
       </c>
       <c r="B140" s="15" t="inlineStr">
         <is>
-          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
+          <t>[Limoges] migration placier</t>
         </is>
       </c>
       <c r="C140" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D140" s="15" t="inlineStr">
         <is>
-          <t>Dijon métropole</t>
+          <t>Limoges</t>
         </is>
       </c>
       <c r="E140" s="15" t="n">
@@ -10644,7 +10672,7 @@
       </c>
       <c r="F140" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G140" s="15" t="inlineStr">
@@ -10654,19 +10682,19 @@
       </c>
       <c r="H140" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I140" s="15" t="inlineStr">
         <is>
-          <t>19/02/2024</t>
+          <t>26/09/2024</t>
         </is>
       </c>
       <c r="J140" s="15" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="K140" s="15" t="n">
-        <v>0.75</v>
+        <v>3.25</v>
       </c>
       <c r="L140" s="15" t="inlineStr"/>
       <c r="M140" s="15" t="inlineStr"/>
@@ -10683,12 +10711,12 @@
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14095</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
@@ -10698,7 +10726,7 @@
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>CC du Pays Sabolien</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E141" s="12" t="n">
@@ -10716,19 +10744,19 @@
       </c>
       <c r="H141" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I141" s="12" t="inlineStr">
         <is>
-          <t>31/01/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J141" s="12" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K141" s="12" t="n">
-        <v>6.75</v>
+        <v>0.25</v>
       </c>
       <c r="L141" s="12" t="inlineStr"/>
       <c r="M141" s="12" t="inlineStr"/>
@@ -10745,12 +10773,12 @@
     <row r="142">
       <c r="A142" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-14551</t>
         </is>
       </c>
       <c r="B142" s="15" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[Perpignan] Interface formulaire</t>
         </is>
       </c>
       <c r="C142" s="15" t="inlineStr">
@@ -10760,7 +10788,7 @@
       </c>
       <c r="D142" s="15" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>[Perpignan]</t>
         </is>
       </c>
       <c r="E142" s="15" t="n">
@@ -10773,7 +10801,7 @@
       </c>
       <c r="G142" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H142" s="15" t="inlineStr">
@@ -10783,25 +10811,17 @@
       </c>
       <c r="I142" s="15" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>14/03/2024</t>
         </is>
       </c>
       <c r="J142" s="15" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="K142" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L142" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M142" s="15" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L142" s="15" t="inlineStr"/>
+      <c r="M142" s="15" t="inlineStr"/>
       <c r="N142" s="16" t="n">
         <v>0</v>
       </c>
@@ -10815,22 +10835,22 @@
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-14254</t>
         </is>
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>Dijon métropole</t>
         </is>
       </c>
       <c r="E143" s="12" t="n">
@@ -10848,19 +10868,19 @@
       </c>
       <c r="H143" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I143" s="12" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>19/02/2024</t>
         </is>
       </c>
       <c r="J143" s="12" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="K143" s="12" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="L143" s="12" t="inlineStr"/>
       <c r="M143" s="12" t="inlineStr"/>
@@ -10877,28 +10897,26 @@
     <row r="144">
       <c r="A144" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12241</t>
+          <t>PDMDEP-14095</t>
         </is>
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
+          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
         </is>
       </c>
       <c r="C144" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D144" s="15" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe]</t>
-        </is>
-      </c>
-      <c r="E144" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement de Littéralis Expert</t>
-        </is>
+          <t>CC du Pays Sabolien</t>
+        </is>
+      </c>
+      <c r="E144" s="15" t="n">
+        <v/>
       </c>
       <c r="F144" s="15" t="inlineStr">
         <is>
@@ -10917,14 +10935,14 @@
       </c>
       <c r="I144" s="15" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>31/01/2024</t>
         </is>
       </c>
       <c r="J144" s="15" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K144" s="15" t="n">
-        <v>0.5</v>
+        <v>7</v>
       </c>
       <c r="L144" s="15" t="inlineStr"/>
       <c r="M144" s="15" t="inlineStr"/>
@@ -10941,12 +10959,12 @@
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B145" s="12" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
@@ -10956,13 +10974,11 @@
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E145" s="12" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>FOUGERES</t>
+        </is>
+      </c>
+      <c r="E145" s="12" t="n">
+        <v/>
       </c>
       <c r="F145" s="12" t="inlineStr">
         <is>
@@ -10971,7 +10987,7 @@
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H145" s="12" t="inlineStr">
@@ -10981,17 +10997,25 @@
       </c>
       <c r="I145" s="12" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J145" s="12" t="n">
         <v>34</v>
       </c>
       <c r="K145" s="12" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="L145" s="12" t="inlineStr"/>
-      <c r="M145" s="12" t="inlineStr"/>
+        <v>2.25</v>
+      </c>
+      <c r="L145" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M145" s="12" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N145" s="13" t="n">
         <v>0</v>
       </c>
@@ -11005,24 +11029,26 @@
     <row r="146">
       <c r="A146" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C146" s="15" t="inlineStr"/>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="C146" s="15" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D146" s="15" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E146" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>LE MANS METROPOLE</t>
+        </is>
+      </c>
+      <c r="E146" s="15" t="n">
+        <v/>
       </c>
       <c r="F146" s="15" t="inlineStr">
         <is>
@@ -11041,14 +11067,14 @@
       </c>
       <c r="I146" s="15" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J146" s="15" t="n">
         <v>34</v>
       </c>
       <c r="K146" s="15" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="L146" s="15" t="inlineStr"/>
       <c r="M146" s="15" t="inlineStr"/>
@@ -11065,21 +11091,29 @@
     <row r="147">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PDMDEP-12241</t>
         </is>
       </c>
       <c r="B147" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="C147" s="12" t="inlineStr"/>
+          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C147" s="12" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="E147" s="12" t="inlineStr"/>
+          <t>[SM Routes de Guadeloupe]</t>
+        </is>
+      </c>
+      <c r="E147" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement de Littéralis Expert</t>
+        </is>
+      </c>
       <c r="F147" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11087,35 +11121,31 @@
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H147" s="12" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H147" s="12" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I147" s="12" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J147" s="12" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="K147" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L147" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M147" s="12" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L147" s="12" t="inlineStr"/>
+      <c r="M147" s="12" t="inlineStr"/>
       <c r="N147" s="13" t="n">
-        <v>510.6</v>
-      </c>
-      <c r="O147" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O147" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P147" s="13" t="n">
@@ -11125,89 +11155,273 @@
     <row r="148">
       <c r="A148" s="14" t="inlineStr">
         <is>
+          <t>PDMDEP-12222</t>
+        </is>
+      </c>
+      <c r="B148" s="15" t="inlineStr">
+        <is>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C148" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D148" s="15" t="inlineStr">
+        <is>
+          <t>CD14</t>
+        </is>
+      </c>
+      <c r="E148" s="15" t="inlineStr">
+        <is>
+          <t>Modélisation spécifique</t>
+        </is>
+      </c>
+      <c r="F148" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G148" s="15" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H148" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I148" s="15" t="inlineStr">
+        <is>
+          <t>04/09/2023</t>
+        </is>
+      </c>
+      <c r="J148" s="15" t="n">
+        <v>34</v>
+      </c>
+      <c r="K148" s="15" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="L148" s="15" t="inlineStr"/>
+      <c r="M148" s="15" t="inlineStr"/>
+      <c r="N148" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O148" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P148" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-11477</t>
+        </is>
+      </c>
+      <c r="B149" s="12" t="inlineStr">
+        <is>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C149" s="12" t="inlineStr"/>
+      <c r="D149" s="12" t="inlineStr">
+        <is>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E149" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
+      <c r="F149" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G149" s="12" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H149" s="12" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I149" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2023</t>
+        </is>
+      </c>
+      <c r="J149" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="K149" s="12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="L149" s="12" t="inlineStr"/>
+      <c r="M149" s="12" t="inlineStr"/>
+      <c r="N149" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O149" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P149" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="14" t="inlineStr">
+        <is>
+          <t>PSC-1270</t>
+        </is>
+      </c>
+      <c r="B150" s="15" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="C150" s="15" t="inlineStr"/>
+      <c r="D150" s="15" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="E150" s="15" t="inlineStr"/>
+      <c r="F150" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G150" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H150" s="15" t="inlineStr"/>
+      <c r="I150" s="15" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J150" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K150" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L150" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M150" s="15" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N150" s="16" t="n">
+        <v>510.6</v>
+      </c>
+      <c r="O150" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P150" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="11" t="inlineStr">
+        <is>
           <t>PSC-1228</t>
         </is>
       </c>
-      <c r="B148" s="15" t="inlineStr">
+      <c r="B151" s="12" t="inlineStr">
         <is>
           <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
-      <c r="C148" s="15" t="inlineStr"/>
-      <c r="D148" s="15" t="inlineStr">
+      <c r="C151" s="12" t="inlineStr"/>
+      <c r="D151" s="12" t="inlineStr">
         <is>
           <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
-      <c r="E148" s="15" t="inlineStr"/>
-      <c r="F148" s="15" t="inlineStr">
+      <c r="E151" s="12" t="inlineStr"/>
+      <c r="F151" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G148" s="15" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H148" s="15" t="inlineStr"/>
-      <c r="I148" s="15" t="inlineStr">
+      <c r="G151" s="12" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H151" s="12" t="inlineStr"/>
+      <c r="I151" s="12" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="J148" s="15" t="n">
+      <c r="J151" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K148" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L148" s="15" t="inlineStr">
+      <c r="K151" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L151" s="12" t="inlineStr">
         <is>
           <t>PDMDEP-32829</t>
         </is>
       </c>
-      <c r="M148" s="15" t="inlineStr">
+      <c r="M151" s="12" t="inlineStr">
         <is>
           <t>00163534</t>
         </is>
       </c>
-      <c r="N148" s="16" t="n">
+      <c r="N151" s="13" t="n">
         <v>50</v>
       </c>
-      <c r="O148" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P148" s="16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="18" t="inlineStr">
+      <c r="O151" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P151" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B149" s="18" t="inlineStr"/>
-      <c r="C149" s="18" t="inlineStr"/>
-      <c r="D149" s="18" t="inlineStr"/>
-      <c r="E149" s="18" t="inlineStr"/>
-      <c r="F149" s="18" t="inlineStr"/>
-      <c r="G149" s="18" t="inlineStr"/>
-      <c r="H149" s="18" t="inlineStr"/>
-      <c r="I149" s="18" t="inlineStr"/>
-      <c r="J149" s="18" t="inlineStr"/>
-      <c r="K149" s="18" t="inlineStr"/>
-      <c r="L149" s="18" t="inlineStr"/>
-      <c r="M149" s="18" t="inlineStr"/>
-      <c r="N149" s="19" t="n">
+      <c r="B152" s="18" t="inlineStr"/>
+      <c r="C152" s="18" t="inlineStr"/>
+      <c r="D152" s="18" t="inlineStr"/>
+      <c r="E152" s="18" t="inlineStr"/>
+      <c r="F152" s="18" t="inlineStr"/>
+      <c r="G152" s="18" t="inlineStr"/>
+      <c r="H152" s="18" t="inlineStr"/>
+      <c r="I152" s="18" t="inlineStr"/>
+      <c r="J152" s="18" t="inlineStr"/>
+      <c r="K152" s="18" t="inlineStr"/>
+      <c r="L152" s="18" t="inlineStr"/>
+      <c r="M152" s="18" t="inlineStr"/>
+      <c r="N152" s="19" t="n">
         <v>68732.95999999999</v>
       </c>
-      <c r="O149" s="19" t="n">
-        <v>10732.88</v>
-      </c>
-      <c r="P149" s="19" t="n">
-        <v>91.17</v>
+      <c r="O152" s="19" t="n">
+        <v>11100.38</v>
+      </c>
+      <c r="P152" s="19" t="n">
+        <v>83.01000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -11357,6 +11571,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A147" r:id="rId143"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId147"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11931,26 +12148,26 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>64.5</v>
+        <v>74</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>21.5</v>
+        <v>24.25</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>0.75</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>86.75</v>
+        <v>99</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>19.75</v>
+        <v>22.25</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>486.15</v>
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>20.4%</t>
         </is>
       </c>
     </row>
@@ -11961,16 +12178,16 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>26.25</v>
+        <v>29.25</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="D6" s="12" t="n">
         <v>0.5</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>29.25</v>
+        <v>33</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>7.5</v>
@@ -11980,7 +12197,7 @@
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -11992,7 +12209,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>46.92</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -12077,10 +12294,10 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>406895</v>
+        <v>410828</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>207091</v>
+        <v>211023</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>199805</v>
@@ -12102,10 +12319,10 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>185691</v>
+        <v>189991</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>78539</v>
+        <v>82839</v>
       </c>
       <c r="D6" s="26" t="n">
         <v>107152</v>
@@ -12127,10 +12344,10 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>221204</v>
+        <v>220836</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>128552</v>
+        <v>128184</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>92652</v>
@@ -12454,7 +12671,7 @@
         </is>
       </c>
       <c r="I9" s="26" t="n">
-        <v>0</v>
+        <v>4300</v>
       </c>
     </row>
     <row r="10">
@@ -12475,7 +12692,7 @@
         </is>
       </c>
       <c r="I10" s="25" t="n">
-        <v>7810</v>
+        <v>12110</v>
       </c>
     </row>
     <row r="11">
@@ -12496,7 +12713,7 @@
         </is>
       </c>
       <c r="I11" s="25" t="n">
-        <v>0</v>
+        <v>4300</v>
       </c>
     </row>
     <row r="12">

--- a/jira_export_2026-07-08.xlsx
+++ b/jira_export_2026-07-08.xlsx
@@ -729,7 +729,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>11,100 €</t>
+          <t>11,820 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -743,7 +743,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -769,7 +769,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>2,419 €</t>
+          <t>3,139 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -824,7 +824,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>219 h</t>
+          <t>233 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -838,7 +838,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>91.2%</t>
+          <t>97.3%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -942,7 +942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P152"/>
+  <dimension ref="A1:P155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1598,7 +1598,7 @@
         <v>1</v>
       </c>
       <c r="K12" s="15" t="n">
-        <v>5</v>
+        <v>7.25</v>
       </c>
       <c r="L12" s="15" t="inlineStr">
         <is>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="N12" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="16" t="n">
-        <v>0</v>
+        <v>1296</v>
+      </c>
+      <c r="O12" s="17" t="n">
+        <v>720</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>0</v>
+        <v>99.31</v>
       </c>
     </row>
     <row r="13">
@@ -2318,7 +2318,7 @@
         <v>1</v>
       </c>
       <c r="K22" s="15" t="n">
-        <v>3.75</v>
+        <v>4.25</v>
       </c>
       <c r="L22" s="15" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>248.58</v>
       </c>
       <c r="P22" s="16" t="n">
-        <v>66.29000000000001</v>
+        <v>58.49</v>
       </c>
     </row>
     <row r="23">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - Crédits 21 heures (3j)</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - Crédits 21 heures (3j)</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C48" s="15" t="inlineStr">
@@ -8058,7 +8058,7 @@
         <v>8</v>
       </c>
       <c r="K102" s="15" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L102" s="15" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>8</v>
       </c>
       <c r="K103" s="12" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L103" s="12" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>8</v>
       </c>
       <c r="K104" s="15" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L104" s="15" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>8</v>
       </c>
       <c r="K105" s="12" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L105" s="12" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>8</v>
       </c>
       <c r="K106" s="15" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L106" s="15" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>9</v>
       </c>
       <c r="K112" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" s="15" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>9</v>
       </c>
       <c r="K113" s="12" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="L113" s="12" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>11</v>
       </c>
       <c r="K117" s="12" t="n">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="L117" s="12" t="inlineStr">
         <is>
@@ -10167,12 +10167,12 @@
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
@@ -10182,7 +10182,7 @@
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E133" s="12" t="n">
@@ -10200,28 +10200,28 @@
       </c>
       <c r="H133" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I133" s="12" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J133" s="12" t="n">
         <v>16</v>
       </c>
       <c r="K133" s="12" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="L133" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27568</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M133" s="12" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N133" s="13" t="n">
@@ -10237,12 +10237,12 @@
     <row r="134">
       <c r="A134" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B134" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C134" s="15" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="D134" s="15" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E134" s="15" t="n">
@@ -10270,28 +10270,28 @@
       </c>
       <c r="H134" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I134" s="15" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J134" s="15" t="n">
         <v>16</v>
       </c>
       <c r="K134" s="15" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="L134" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27377</t>
+          <t>PDMDEP-27568</t>
         </is>
       </c>
       <c r="M134" s="15" t="inlineStr">
         <is>
-          <t>478048</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="N134" s="16" t="n">
@@ -10307,12 +10307,12 @@
     <row r="135">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-19385</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B135" s="12" t="inlineStr">
         <is>
-          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
@@ -10322,7 +10322,7 @@
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARCUEIL</t>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
         </is>
       </c>
       <c r="E135" s="12" t="n">
@@ -10345,23 +10345,23 @@
       </c>
       <c r="I135" s="12" t="inlineStr">
         <is>
-          <t>24/02/2025</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J135" s="12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K135" s="12" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L135" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27535</t>
+          <t>PDMDEP-27377</t>
         </is>
       </c>
       <c r="M135" s="12" t="inlineStr">
         <is>
-          <t>465345</t>
+          <t>478048</t>
         </is>
       </c>
       <c r="N135" s="13" t="n">
@@ -10377,12 +10377,12 @@
     <row r="136">
       <c r="A136" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-19385</t>
         </is>
       </c>
       <c r="B136" s="15" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
         </is>
       </c>
       <c r="C136" s="15" t="inlineStr">
@@ -10392,7 +10392,7 @@
       </c>
       <c r="D136" s="15" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>COMMUNE D'ARCUEIL</t>
         </is>
       </c>
       <c r="E136" s="15" t="n">
@@ -10405,7 +10405,7 @@
       </c>
       <c r="G136" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H136" s="15" t="inlineStr">
@@ -10415,17 +10415,25 @@
       </c>
       <c r="I136" s="15" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>24/02/2025</t>
         </is>
       </c>
       <c r="J136" s="15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K136" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="L136" s="15" t="inlineStr"/>
-      <c r="M136" s="15" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L136" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27535</t>
+        </is>
+      </c>
+      <c r="M136" s="15" t="inlineStr">
+        <is>
+          <t>465345</t>
+        </is>
+      </c>
       <c r="N136" s="16" t="n">
         <v>0</v>
       </c>
@@ -10439,22 +10447,22 @@
     <row r="137">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E137" s="12" t="n">
@@ -10462,44 +10470,36 @@
       </c>
       <c r="F137" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H137" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I137" s="12" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J137" s="12" t="n">
         <v>19</v>
       </c>
       <c r="K137" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L137" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M137" s="12" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="L137" s="12" t="inlineStr"/>
+      <c r="M137" s="12" t="inlineStr"/>
       <c r="N137" s="13" t="n">
-        <v>240</v>
-      </c>
-      <c r="O137" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P137" s="13" t="n">
@@ -10509,22 +10509,22 @@
     <row r="138">
       <c r="A138" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C138" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D138" s="15" t="inlineStr">
         <is>
-          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E138" s="15" t="n">
@@ -10532,7 +10532,7 @@
       </c>
       <c r="F138" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G138" s="15" t="inlineStr">
@@ -10542,34 +10542,34 @@
       </c>
       <c r="H138" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I138" s="15" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J138" s="15" t="n">
         <v>19</v>
       </c>
       <c r="K138" s="15" t="n">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="L138" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34362</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M138" s="15" t="inlineStr">
         <is>
-          <t>458057</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N138" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O138" s="16" t="n">
+        <v>240</v>
+      </c>
+      <c r="O138" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P138" s="16" t="n">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
         </is>
       </c>
       <c r="E139" s="12" t="n">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="L139" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28020</t>
+          <t>PDMDEP-34362</t>
         </is>
       </c>
       <c r="M139" s="12" t="inlineStr">
@@ -10649,22 +10649,22 @@
     <row r="140">
       <c r="A140" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-16868</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B140" s="15" t="inlineStr">
         <is>
-          <t>[Limoges] migration placier</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C140" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D140" s="15" t="inlineStr">
         <is>
-          <t>Limoges</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E140" s="15" t="n">
@@ -10672,32 +10672,40 @@
       </c>
       <c r="F140" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G140" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H140" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I140" s="15" t="inlineStr">
         <is>
-          <t>26/09/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J140" s="15" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K140" s="15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L140" s="15" t="inlineStr"/>
-      <c r="M140" s="15" t="inlineStr"/>
+        <v>0.62</v>
+      </c>
+      <c r="L140" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28020</t>
+        </is>
+      </c>
+      <c r="M140" s="15" t="inlineStr">
+        <is>
+          <t>458057</t>
+        </is>
+      </c>
       <c r="N140" s="16" t="n">
         <v>0</v>
       </c>
@@ -10711,22 +10719,22 @@
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-16868</t>
         </is>
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[Limoges] migration placier</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>Limoges</t>
         </is>
       </c>
       <c r="E141" s="12" t="n">
@@ -10734,7 +10742,7 @@
       </c>
       <c r="F141" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G141" s="12" t="inlineStr">
@@ -10744,19 +10752,19 @@
       </c>
       <c r="H141" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I141" s="12" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>26/09/2024</t>
         </is>
       </c>
       <c r="J141" s="12" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K141" s="12" t="n">
-        <v>0.25</v>
+        <v>3.25</v>
       </c>
       <c r="L141" s="12" t="inlineStr"/>
       <c r="M141" s="12" t="inlineStr"/>
@@ -10773,22 +10781,22 @@
     <row r="142">
       <c r="A142" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14551</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B142" s="15" t="inlineStr">
         <is>
-          <t>[Perpignan] Interface formulaire</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C142" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D142" s="15" t="inlineStr">
         <is>
-          <t>[Perpignan]</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E142" s="15" t="n">
@@ -10811,14 +10819,14 @@
       </c>
       <c r="I142" s="15" t="inlineStr">
         <is>
-          <t>14/03/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J142" s="15" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K142" s="15" t="n">
-        <v>1.25</v>
+        <v>0.25</v>
       </c>
       <c r="L142" s="15" t="inlineStr"/>
       <c r="M142" s="15" t="inlineStr"/>
@@ -10835,12 +10843,12 @@
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14254</t>
+          <t>PDMDEP-14551</t>
         </is>
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
-          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
+          <t>[Perpignan] Interface formulaire</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
@@ -10850,7 +10858,7 @@
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>Dijon métropole</t>
+          <t>[Perpignan]</t>
         </is>
       </c>
       <c r="E143" s="12" t="n">
@@ -10873,14 +10881,14 @@
       </c>
       <c r="I143" s="12" t="inlineStr">
         <is>
-          <t>19/02/2024</t>
+          <t>14/03/2024</t>
         </is>
       </c>
       <c r="J143" s="12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K143" s="12" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="L143" s="12" t="inlineStr"/>
       <c r="M143" s="12" t="inlineStr"/>
@@ -10897,22 +10905,22 @@
     <row r="144">
       <c r="A144" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14095</t>
+          <t>PDMDEP-14254</t>
         </is>
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
+          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
         </is>
       </c>
       <c r="C144" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D144" s="15" t="inlineStr">
         <is>
-          <t>CC du Pays Sabolien</t>
+          <t>Dijon métropole</t>
         </is>
       </c>
       <c r="E144" s="15" t="n">
@@ -10930,19 +10938,19 @@
       </c>
       <c r="H144" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I144" s="15" t="inlineStr">
         <is>
-          <t>31/01/2024</t>
+          <t>19/02/2024</t>
         </is>
       </c>
       <c r="J144" s="15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K144" s="15" t="n">
-        <v>7</v>
+        <v>0.75</v>
       </c>
       <c r="L144" s="15" t="inlineStr"/>
       <c r="M144" s="15" t="inlineStr"/>
@@ -10959,22 +10967,22 @@
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-14095</t>
         </is>
       </c>
       <c r="B145" s="12" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>CC du Pays Sabolien</t>
         </is>
       </c>
       <c r="E145" s="12" t="n">
@@ -10987,35 +10995,27 @@
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H145" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I145" s="12" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>31/01/2024</t>
         </is>
       </c>
       <c r="J145" s="12" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K145" s="12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L145" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M145" s="12" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>7.25</v>
+      </c>
+      <c r="L145" s="12" t="inlineStr"/>
+      <c r="M145" s="12" t="inlineStr"/>
       <c r="N145" s="13" t="n">
         <v>0</v>
       </c>
@@ -11029,22 +11029,22 @@
     <row r="146">
       <c r="A146" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C146" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D146" s="15" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E146" s="15" t="n">
@@ -11057,27 +11057,35 @@
       </c>
       <c r="G146" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H146" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I146" s="15" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J146" s="15" t="n">
         <v>34</v>
       </c>
       <c r="K146" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L146" s="15" t="inlineStr"/>
-      <c r="M146" s="15" t="inlineStr"/>
+        <v>2.25</v>
+      </c>
+      <c r="L146" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M146" s="15" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N146" s="16" t="n">
         <v>0</v>
       </c>
@@ -11091,28 +11099,26 @@
     <row r="147">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12241</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B147" s="12" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe]</t>
-        </is>
-      </c>
-      <c r="E147" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement de Littéralis Expert</t>
-        </is>
+          <t>CD 56 MORBIHAN</t>
+        </is>
+      </c>
+      <c r="E147" s="12" t="n">
+        <v/>
       </c>
       <c r="F147" s="12" t="inlineStr">
         <is>
@@ -11121,17 +11127,13 @@
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H147" s="12" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H147" s="12" t="inlineStr"/>
       <c r="I147" s="12" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J147" s="12" t="n">
@@ -11155,28 +11157,26 @@
     <row r="148">
       <c r="A148" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C148" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D148" s="15" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E148" s="15" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>LE MANS METROPOLE</t>
+        </is>
+      </c>
+      <c r="E148" s="15" t="n">
+        <v/>
       </c>
       <c r="F148" s="15" t="inlineStr">
         <is>
@@ -11190,19 +11190,19 @@
       </c>
       <c r="H148" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I148" s="15" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J148" s="15" t="n">
         <v>34</v>
       </c>
       <c r="K148" s="15" t="n">
-        <v>8.75</v>
+        <v>1</v>
       </c>
       <c r="L148" s="15" t="inlineStr"/>
       <c r="M148" s="15" t="inlineStr"/>
@@ -11219,24 +11219,26 @@
     <row r="149">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12443</t>
         </is>
       </c>
       <c r="B149" s="12" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C149" s="12" t="inlineStr"/>
+          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C149" s="12" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E149" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>CD79 - Deux Sèvres</t>
+        </is>
+      </c>
+      <c r="E149" s="12" t="n">
+        <v/>
       </c>
       <c r="F149" s="12" t="inlineStr">
         <is>
@@ -11255,14 +11257,14 @@
       </c>
       <c r="I149" s="12" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J149" s="12" t="n">
         <v>34</v>
       </c>
       <c r="K149" s="12" t="n">
-        <v>1.75</v>
+        <v>0.5</v>
       </c>
       <c r="L149" s="12" t="inlineStr"/>
       <c r="M149" s="12" t="inlineStr"/>
@@ -11279,21 +11281,29 @@
     <row r="150">
       <c r="A150" s="14" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PDMDEP-12241</t>
         </is>
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="C150" s="15" t="inlineStr"/>
+          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C150" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D150" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="E150" s="15" t="inlineStr"/>
+          <t>[SM Routes de Guadeloupe]</t>
+        </is>
+      </c>
+      <c r="E150" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement de Littéralis Expert</t>
+        </is>
+      </c>
       <c r="F150" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11301,35 +11311,31 @@
       </c>
       <c r="G150" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H150" s="15" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H150" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I150" s="15" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J150" s="15" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="K150" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L150" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M150" s="15" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L150" s="15" t="inlineStr"/>
+      <c r="M150" s="15" t="inlineStr"/>
       <c r="N150" s="16" t="n">
-        <v>510.6</v>
-      </c>
-      <c r="O150" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O150" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P150" s="16" t="n">
@@ -11339,89 +11345,273 @@
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
         <is>
+          <t>PDMDEP-12222</t>
+        </is>
+      </c>
+      <c r="B151" s="12" t="inlineStr">
+        <is>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C151" s="12" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D151" s="12" t="inlineStr">
+        <is>
+          <t>CD14</t>
+        </is>
+      </c>
+      <c r="E151" s="12" t="inlineStr">
+        <is>
+          <t>Modélisation spécifique</t>
+        </is>
+      </c>
+      <c r="F151" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G151" s="12" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H151" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I151" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2023</t>
+        </is>
+      </c>
+      <c r="J151" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="K151" s="12" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="L151" s="12" t="inlineStr"/>
+      <c r="M151" s="12" t="inlineStr"/>
+      <c r="N151" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O151" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P151" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-11477</t>
+        </is>
+      </c>
+      <c r="B152" s="15" t="inlineStr">
+        <is>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C152" s="15" t="inlineStr"/>
+      <c r="D152" s="15" t="inlineStr">
+        <is>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E152" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
+      <c r="F152" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G152" s="15" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H152" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I152" s="15" t="inlineStr">
+        <is>
+          <t>03/09/2023</t>
+        </is>
+      </c>
+      <c r="J152" s="15" t="n">
+        <v>34</v>
+      </c>
+      <c r="K152" s="15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="L152" s="15" t="inlineStr"/>
+      <c r="M152" s="15" t="inlineStr"/>
+      <c r="N152" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O152" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P152" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="11" t="inlineStr">
+        <is>
+          <t>PSC-1270</t>
+        </is>
+      </c>
+      <c r="B153" s="12" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="C153" s="12" t="inlineStr"/>
+      <c r="D153" s="12" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="E153" s="12" t="inlineStr"/>
+      <c r="F153" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G153" s="12" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H153" s="12" t="inlineStr"/>
+      <c r="I153" s="12" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J153" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K153" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M153" s="12" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N153" s="13" t="n">
+        <v>510.6</v>
+      </c>
+      <c r="O153" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P153" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="14" t="inlineStr">
+        <is>
           <t>PSC-1228</t>
         </is>
       </c>
-      <c r="B151" s="12" t="inlineStr">
+      <c r="B154" s="15" t="inlineStr">
         <is>
           <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
-      <c r="C151" s="12" t="inlineStr"/>
-      <c r="D151" s="12" t="inlineStr">
+      <c r="C154" s="15" t="inlineStr"/>
+      <c r="D154" s="15" t="inlineStr">
         <is>
           <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
-      <c r="E151" s="12" t="inlineStr"/>
-      <c r="F151" s="12" t="inlineStr">
+      <c r="E154" s="15" t="inlineStr"/>
+      <c r="F154" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G151" s="12" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H151" s="12" t="inlineStr"/>
-      <c r="I151" s="12" t="inlineStr">
+      <c r="G154" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H154" s="15" t="inlineStr"/>
+      <c r="I154" s="15" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="J151" s="12" t="n">
+      <c r="J154" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="K151" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L151" s="12" t="inlineStr">
+      <c r="K154" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L154" s="15" t="inlineStr">
         <is>
           <t>PDMDEP-32829</t>
         </is>
       </c>
-      <c r="M151" s="12" t="inlineStr">
+      <c r="M154" s="15" t="inlineStr">
         <is>
           <t>00163534</t>
         </is>
       </c>
-      <c r="N151" s="13" t="n">
+      <c r="N154" s="16" t="n">
         <v>50</v>
       </c>
-      <c r="O151" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P151" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="18" t="inlineStr">
+      <c r="O154" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B152" s="18" t="inlineStr"/>
-      <c r="C152" s="18" t="inlineStr"/>
-      <c r="D152" s="18" t="inlineStr"/>
-      <c r="E152" s="18" t="inlineStr"/>
-      <c r="F152" s="18" t="inlineStr"/>
-      <c r="G152" s="18" t="inlineStr"/>
-      <c r="H152" s="18" t="inlineStr"/>
-      <c r="I152" s="18" t="inlineStr"/>
-      <c r="J152" s="18" t="inlineStr"/>
-      <c r="K152" s="18" t="inlineStr"/>
-      <c r="L152" s="18" t="inlineStr"/>
-      <c r="M152" s="18" t="inlineStr"/>
-      <c r="N152" s="19" t="n">
-        <v>68732.95999999999</v>
-      </c>
-      <c r="O152" s="19" t="n">
-        <v>11100.38</v>
-      </c>
-      <c r="P152" s="19" t="n">
-        <v>83.01000000000001</v>
+      <c r="B155" s="18" t="inlineStr"/>
+      <c r="C155" s="18" t="inlineStr"/>
+      <c r="D155" s="18" t="inlineStr"/>
+      <c r="E155" s="18" t="inlineStr"/>
+      <c r="F155" s="18" t="inlineStr"/>
+      <c r="G155" s="18" t="inlineStr"/>
+      <c r="H155" s="18" t="inlineStr"/>
+      <c r="I155" s="18" t="inlineStr"/>
+      <c r="J155" s="18" t="inlineStr"/>
+      <c r="K155" s="18" t="inlineStr"/>
+      <c r="L155" s="18" t="inlineStr"/>
+      <c r="M155" s="18" t="inlineStr"/>
+      <c r="N155" s="19" t="n">
+        <v>70028.95999999999</v>
+      </c>
+      <c r="O155" s="19" t="n">
+        <v>11820.38</v>
+      </c>
+      <c r="P155" s="19" t="n">
+        <v>82.81999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -11574,6 +11764,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId145"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId146"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId150"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12148,26 +12341,26 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>74</v>
+        <v>82.25</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>24.25</v>
+        <v>25</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>0.75</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>22.25</v>
+        <v>24.5</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>486.15</v>
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
     </row>
@@ -12209,7 +12402,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>53</v>
+        <v>56.08</v>
       </c>
     </row>
   </sheetData>
@@ -12294,10 +12487,10 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>410828</v>
+        <v>410108</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>211023</v>
+        <v>210303</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>199805</v>
@@ -12319,10 +12512,10 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>189991</v>
+        <v>189271</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>82839</v>
+        <v>82119</v>
       </c>
       <c r="D6" s="26" t="n">
         <v>107152</v>
